--- a/Text2SQL_Template/output/ddq_autogen_customer.xlsx
+++ b/Text2SQL_Template/output/ddq_autogen_customer.xlsx
@@ -184,79 +184,433 @@
     <t>Tìm kiếm chính xác bản ghi dựa trên unique_image_back</t>
   </si>
   <si>
-    <t>Kiểm tra lệnh chuyển tiền với mã {{{id}}}|Hiển thị lệnh chuyển tiền mang id {{{id}}}|Xem chi tiết biến động số dư theo primary key {{{id}}}|Tìm history với id tự tăng, khóa chính {{{id}}}|Search giao dịch của mã {{{id}}}|Tìm biến động số dư theo id tự tăng, khóa chính {{{id}}}|Kiểm tra biến động số dư với id {{{id}}}|Hiển thị biến động số dư với id {{{id}}}|Xem chi tiết history tại primary key {{{id}}}|Tra cứu biến động số dư với id {{{id}}}|Liệt kê lệnh chuyển tiền với số {{{id}}}|Liệt kê history của mã {{{id}}}|Search lệnh chuyển tiền tại id tự tăng, khóa chính {{{id}}}|Tìm biến động số dư theo primary key {{{id}}}|Cho tôi xem giao dịch có số {{{id}}}</t>
-  </si>
-  <si>
-    <t>Hiển thị biến động số dư theo số cif {{{cif_no}}}|Kiểm tra biến động số dư tại customer information file {{{cif_no}}}|Cho tôi xem history của số cif {{{cif_no}}}|Hiển thị lệnh chuyển tiền có số cif {{{cif_no}}}|Hiển thị giao dịch với customer information file {{{cif_no}}}|Cho tôi xem giao dịch tại customer information file {{{cif_no}}}|Search history mang số cif {{{cif_no}}}|Tra cứu lệnh chuyển tiền của customer information file {{{cif_no}}}|Search lệnh chuyển tiền với số cif {{{cif_no}}}|Tìm lệnh chuyển tiền tại số cif {{{cif_no}}}|Tìm giao dịch với số cif {{{cif_no}}}|Liệt kê giao dịch theo số cif {{{cif_no}}}|Liệt kê lệnh chuyển tiền theo customer information file {{{cif_no}}}|Liệt kê lệnh chuyển tiền mang số cif {{{cif_no}}}|Liệt kê giao dịch có số cif {{{cif_no}}}</t>
-  </si>
-  <si>
-    <t>Hiển thị biến động số dư mang id định danh khách hàng nội bộ. {{{customer_id}}}|Kiểm tra lệnh chuyển tiền với mã {{{customer_id}}}|Hiển thị lệnh chuyển tiền mang id {{{customer_id}}}|Search giao dịch của mã {{{customer_id}}}|Kiểm tra biến động số dư với id {{{customer_id}}}|Hiển thị biến động số dư với id {{{customer_id}}}|Tra cứu biến động số dư với id {{{customer_id}}}|Liệt kê lệnh chuyển tiền với số {{{customer_id}}}|Liệt kê history của mã {{{customer_id}}}|Cho tôi xem giao dịch có số {{{customer_id}}}|Kiểm tra biến động số dư tại mã {{{customer_id}}}|Search biến động số dư theo mã {{{customer_id}}}|Kiểm tra biến động số dư mang id {{{customer_id}}}|Cho tôi xem lệnh chuyển tiền của id định danh khách hàng nội bộ. {{{customer_id}}}|Search lệnh chuyển tiền mang mã {{{customer_id}}}</t>
-  </si>
-  <si>
-    <t>Hiển thị history của mã số khách hàng {{{customer_no}}}|Kiểm tra history mang mã số khách hàng {{{customer_no}}}|Hiển thị lệnh chuyển tiền theo có thể khác với cif tùy theo cấu trúc hệ thống {{{customer_no}}}|Search history có mã số khách hàng {{{customer_no}}}|Cho tôi xem giao dịch của có thể khác với cif tùy theo cấu trúc hệ thống {{{customer_no}}}|Search biến động số dư của mã số khách hàng {{{customer_no}}}|Tìm giao dịch tại có thể khác với cif tùy theo cấu trúc hệ thống {{{customer_no}}}|Liệt kê lệnh chuyển tiền với mã số khách hàng {{{customer_no}}}|Tìm giao dịch mang có thể khác với cif tùy theo cấu trúc hệ thống {{{customer_no}}}|Search lệnh chuyển tiền theo có thể khác với cif tùy theo cấu trúc hệ thống {{{customer_no}}}|Kiểm tra lệnh chuyển tiền mang có thể khác với cif tùy theo cấu trúc hệ thống {{{customer_no}}}|Xem chi tiết history có mã số khách hàng {{{customer_no}}}|Search giao dịch có mã số khách hàng {{{customer_no}}}|Kiểm tra giao dịch tại có thể khác với cif tùy theo cấu trúc hệ thống {{{customer_no}}}|Xem chi tiết lệnh chuyển tiền với có thể khác với cif tùy theo cấu trúc hệ thống {{{customer_no}}}</t>
-  </si>
-  <si>
-    <t>Kiểm tra lệnh chuyển tiền với mã {{{system_id}}}|Hiển thị lệnh chuyển tiền mang id {{{system_id}}}|Search giao dịch của mã {{{system_id}}}|Cho tôi xem history tại nếu dữ liệu được đẩy từ khác sang {{{system_id}}}|Tìm giao dịch mang id nguồn {{{system_id}}}|Tìm lệnh chuyển tiền mang nếu dữ liệu được đẩy từ khác sang {{{system_id}}}|Kiểm tra biến động số dư với id {{{system_id}}}|Hiển thị biến động số dư với id {{{system_id}}}|Hiển thị biến động số dư có nếu dữ liệu được đẩy từ khác sang {{{system_id}}}|Xem chi tiết lệnh chuyển tiền có nếu dữ liệu được đẩy từ khác sang {{{system_id}}}|Tra cứu biến động số dư với id {{{system_id}}}|Liệt kê lệnh chuyển tiền với số {{{system_id}}}|Liệt kê history của mã {{{system_id}}}|Tìm biến động số dư có nếu dữ liệu được đẩy từ khác sang {{{system_id}}}|Cho tôi xem giao dịch có số {{{system_id}}}</t>
-  </si>
-  <si>
-    <t>Cho tôi xem history của chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}|Tra cứu biến động số dư theo chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}|Tìm history với chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}|Xem chi tiết giao dịch có chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}|Tìm history có chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}|Search history theo chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}|Tìm lệnh chuyển tiền theo chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}|Liệt kê history với chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}|Hiển thị giao dịch mang chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}|Kiểm tra lệnh chuyển tiền có chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}|Cho tôi xem biến động số dư mang chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}|Xem chi tiết lệnh chuyển tiền của chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}|Liệt kê biến động số dư có chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}|Search biến động số dư theo chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}|Search history với chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}</t>
-  </si>
-  <si>
-    <t>Danh sách lệnh chuyển tiền theo hình thức {{{cif_type}}}|Các giao dịch của loại cif {{{cif_type}}}|Các giao dịch có ví dụ: cá nhân, doanh nghiệp, khách hàng ưu tiên... {{{cif_type}}}|Danh sách biến động số dư theo loại {{{cif_type}}}|Danh sách history tại ví dụ: cá nhân, doanh nghiệp, khách hàng ưu tiên... {{{cif_type}}}|Các lệnh chuyển tiền theo hình thức {{{cif_type}}}|Danh sách giao dịch có hình thức {{{cif_type}}}|Lọc các history với ví dụ: cá nhân, doanh nghiệp, khách hàng ưu tiên... {{{cif_type}}}|Lọc các history mang loại cif {{{cif_type}}}|Danh sách giao dịch tại hình thức {{{cif_type}}}|Các history có loại cif {{{cif_type}}}|Các giao dịch với hình thức {{{cif_type}}}|Những biến động số dư tại loại cif {{{cif_type}}}|Những biến động số dư tại loại {{{cif_type}}}|Danh sách lệnh chuyển tiền có ví dụ: cá nhân, doanh nghiệp, khách hàng ưu tiên... {{{cif_type}}}</t>
-  </si>
-  <si>
-    <t>Tìm history có mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}|Tra cứu history tại mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}|Liệt kê history tại mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}|Kiểm tra giao dịch với mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}|Xem chi tiết lệnh chuyển tiền theo mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}|Xem chi tiết history với mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}|Kiểm tra history với mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}|Xem chi tiết giao dịch của mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}|Xem chi tiết giao dịch mang mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}|Tra cứu giao dịch của mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}|Tìm giao dịch có mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}|Hiển thị lệnh chuyển tiền có mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}|Liệt kê biến động số dư của mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}|Hiển thị lệnh chuyển tiền với mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}|Hiển thị history mang mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}</t>
-  </si>
-  <si>
-    <t>Lọc các biến động số dư mang trạng thái hiện tại khách hàng {{{customer_status}}}|Lọc các lệnh chuyển tiền với trạng thái {{{customer_status}}}|Các giao dịch có active, inactive, closed... {{{customer_status}}}|Các biến động số dư tại tình trạng {{{customer_status}}}|Các history của trạng thái hiện tại khách hàng {{{customer_status}}}|Những giao dịch theo kết quả {{{customer_status}}}|Danh sách history với trạng thái hiện tại khách hàng {{{customer_status}}}|Danh sách history tại active, inactive, closed... {{{customer_status}}}|Những biến động số dư mang trạng thái hiện tại khách hàng {{{customer_status}}}|Các lệnh chuyển tiền theo tình trạng {{{customer_status}}}|Những biến động số dư của trạng thái {{{customer_status}}}|Danh sách history tại tình trạng {{{customer_status}}}|Danh sách giao dịch có trạng thái {{{customer_status}}}|Danh sách lệnh chuyển tiền với active, inactive, closed... {{{customer_status}}}|Lọc các giao dịch với trạng thái {{{customer_status}}}</t>
-  </si>
-  <si>
-    <t>Search lệnh chuyển tiền mang ngày cấp giấy tờ định danh {{{date_of_issue}}}|Hiển thị biến động số dư với cmnd/cccd/hộ chiếu {{{date_of_issue}}}|Xem chi tiết biến động số dư có cmnd/cccd/hộ chiếu {{{date_of_issue}}}|Kiểm tra lệnh chuyển tiền có cmnd/cccd/hộ chiếu {{{date_of_issue}}}|Kiểm tra giao dịch của cmnd/cccd/hộ chiếu {{{date_of_issue}}}|Tra cứu giao dịch của ngày cấp giấy tờ định danh {{{date_of_issue}}}|Hiển thị biến động số dư theo ngày cấp giấy tờ định danh {{{date_of_issue}}}|Search giao dịch của ngày cấp giấy tờ định danh {{{date_of_issue}}}|Search giao dịch với cmnd/cccd/hộ chiếu {{{date_of_issue}}}|Search giao dịch tại ngày cấp giấy tờ định danh {{{date_of_issue}}}|Hiển thị history mang ngày cấp giấy tờ định danh {{{date_of_issue}}}|Tra cứu biến động số dư của ngày cấp giấy tờ định danh {{{date_of_issue}}}|Xem chi tiết giao dịch theo ngày cấp giấy tờ định danh {{{date_of_issue}}}|Tra cứu lệnh chuyển tiền của cmnd/cccd/hộ chiếu {{{date_of_issue}}}|Xem chi tiết biến động số dư theo ngày cấp giấy tờ định danh {{{date_of_issue}}}</t>
-  </si>
-  <si>
-    <t>Tra cứu lệnh chuyển tiền với số cmnd, cccd hoặc hộ chiếu {{{identify_id}}}|Kiểm tra lệnh chuyển tiền với mã {{{identify_id}}}|Hiển thị lệnh chuyển tiền mang id {{{identify_id}}}|Tra cứu lệnh chuyển tiền theo số cmnd, cccd hoặc hộ chiếu {{{identify_id}}}|Tra cứu history tại số cmnd, cccd hoặc hộ chiếu {{{identify_id}}}|Hiển thị giao dịch tại số cmnd, cccd hoặc hộ chiếu {{{identify_id}}}|Search giao dịch của mã {{{identify_id}}}|Xem chi tiết biến động số dư tại số cmnd, cccd hoặc hộ chiếu {{{identify_id}}}|Kiểm tra biến động số dư với id {{{identify_id}}}|Hiển thị biến động số dư với id {{{identify_id}}}|Cho tôi xem lệnh chuyển tiền mang số giấy tờ định danh {{{identify_id}}}|Tra cứu giao dịch có số giấy tờ định danh {{{identify_id}}}|Tra cứu biến động số dư với id {{{identify_id}}}|Liệt kê lệnh chuyển tiền với số {{{identify_id}}}|Cho tôi xem history tại số cmnd, cccd hoặc hộ chiếu {{{identify_id}}}</t>
-  </si>
-  <si>
-    <t>Xem chi tiết biến động số dư với ví dụ: đã xác thực - ekyc, chưa xác thực {{{identify_level}}}|Tìm lệnh chuyển tiền theo ví dụ: đã xác thực - ekyc, chưa xác thực {{{identify_level}}}|Kiểm tra lệnh chuyển tiền với mã {{{identify_level}}}|Hiển thị lệnh chuyển tiền mang id {{{identify_level}}}|Hiển thị lệnh chuyển tiền của ví dụ: đã xác thực - ekyc, chưa xác thực {{{identify_level}}}|Search giao dịch của mã {{{identify_level}}}|Kiểm tra biến động số dư với id {{{identify_level}}}|Hiển thị biến động số dư với id {{{identify_level}}}|Search lệnh chuyển tiền tại cấp độ định danh {{{identify_level}}}|Tra cứu biến động số dư với id {{{identify_level}}}|Liệt kê giao dịch của cấp độ định danh {{{identify_level}}}|Hiển thị history có ví dụ: đã xác thực - ekyc, chưa xác thực {{{identify_level}}}|Liệt kê lệnh chuyển tiền với số {{{identify_level}}}|Liệt kê history của mã {{{identify_level}}}|Search giao dịch có ví dụ: đã xác thực - ekyc, chưa xác thực {{{identify_level}}}</t>
-  </si>
-  <si>
-    <t>Kiểm tra lệnh chuyển tiền với mã {{{identify_name}}}|Hiển thị history của ví dụ: "identity card", "passport" {{{identify_name}}}|Cho tôi xem history mang ví dụ: "identity card", "passport" {{{identify_name}}}|Kiểm tra giao dịch tại ví dụ: "identity card", "passport" {{{identify_name}}}|Hiển thị lệnh chuyển tiền mang id {{{identify_name}}}|Xem chi tiết giao dịch với ví dụ: "identity card", "passport" {{{identify_name}}}|Search giao dịch của mã {{{identify_name}}}|Kiểm tra biến động số dư với id {{{identify_name}}}|Hiển thị biến động số dư với id {{{identify_name}}}|Tra cứu biến động số dư với id {{{identify_name}}}|Liệt kê lệnh chuyển tiền với số {{{identify_name}}}|Liệt kê history của mã {{{identify_name}}}|Search biến động số dư với loại giấy tờ định danh {{{identify_name}}}|Cho tôi xem giao dịch có số {{{identify_name}}}|Kiểm tra biến động số dư tại mã {{{identify_name}}}</t>
-  </si>
-  <si>
-    <t>Sao kê giao dịch từ ngày {{start_date}} đến {{end_date}}|Liệt kê lịch sử trong khoảng thời gian {{start_date}} - {{end_date}}|Kiểm tra giao dịch phát sinh từ {{start_date}} tới {{end_date}}|Cho tôi xem biến động số dư giữa {{start_date}} và {{end_date}}</t>
-  </si>
-  <si>
-    <t>Tính tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. của các giao dịch có cif_type là {{cif_type}}|Xem tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. theo cif_type {{cif_type}}|Tính tổng phí của các giao dịch có cif_type là {{cif_type}}|Xem tổng phí theo cif_type {{cif_type}}|Tính tổng tiền phí của các giao dịch có cif_type là {{cif_type}}|Xem tổng tiền phí theo cif_type {{cif_type}}|Tổng cộng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. của các giao dịch có cif_type là {{cif_type}}|Xem tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. theo cif_type {{cif_type}}|Tổng cộng phí của các giao dịch có cif_type là {{cif_type}}|Xem tổng phí theo cif_type {{cif_type}}|Tổng cộng tiền phí của các giao dịch có cif_type là {{cif_type}}|Xem tổng tiền phí theo cif_type {{cif_type}}|Thống kê đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. của các giao dịch có cif_type là {{cif_type}}|Xem tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. theo cif_type {{cif_type}}|Thống kê phí của các giao dịch có cif_type là {{cif_type}}|Xem tổng phí theo cif_type {{cif_type}}|Thống kê tiền phí của các giao dịch có cif_type là {{cif_type}}|Xem tổng tiền phí theo cif_type {{cif_type}}|Cộng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. của các giao dịch có cif_type là {{cif_type}}|Xem tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. theo cif_type {{cif_type}}|Cộng phí của các giao dịch có cif_type là {{cif_type}}|Xem tổng phí theo cif_type {{cif_type}}|Cộng tiền phí của các giao dịch có cif_type là {{cif_type}}|Xem tổng tiền phí theo cif_type {{cif_type}}|Xem tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. của các giao dịch có cif_type là {{cif_type}}|Xem tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. theo cif_type {{cif_type}}|Xem tổng phí của các giao dịch có cif_type là {{cif_type}}|Xem tổng phí theo cif_type {{cif_type}}|Xem tổng tiền phí của các giao dịch có cif_type là {{cif_type}}|Xem tổng tiền phí theo cif_type {{cif_type}}</t>
-  </si>
-  <si>
-    <t>Xem chi tiết lệnh chuyển tiền với ví dụ: vn, us, jp {{{nationality_id}}}|Kiểm tra lệnh chuyển tiền với mã {{{nationality_id}}}|Xem chi tiết biến động số dư mang ví dụ: vn, us, jp {{{nationality_id}}}|Cho tôi xem biến động số dư theo ví dụ: vn, us, jp {{{nationality_id}}}|Hiển thị lệnh chuyển tiền mang id {{{nationality_id}}}|Cho tôi xem history có mã quốc tịch {{{nationality_id}}}|Search giao dịch của mã {{{nationality_id}}}|Kiểm tra biến động số dư với id {{{nationality_id}}}|Hiển thị biến động số dư với id {{{nationality_id}}}|Liệt kê biến động số dư mang mã quốc tịch {{{nationality_id}}}|Tìm giao dịch tại ví dụ: vn, us, jp {{{nationality_id}}}|Liệt kê biến động số dư mang ví dụ: vn, us, jp {{{nationality_id}}}|Tra cứu biến động số dư với id {{{nationality_id}}}|Kiểm tra lệnh chuyển tiền tại ví dụ: vn, us, jp {{{nationality_id}}}|Liệt kê lệnh chuyển tiền với số {{{nationality_id}}}</t>
-  </si>
-  <si>
-    <t>Kiểm tra lệnh chuyển tiền với mã {{{place_id}}}|Hiển thị lệnh chuyển tiền mang id {{{place_id}}}|Hiển thị biến động số dư của mã vùng/địa điểm cư trú. {{{place_id}}}|Kiểm tra lệnh chuyển tiền mang mã vùng/địa điểm cư trú. {{{place_id}}}|Search giao dịch của mã {{{place_id}}}|Kiểm tra biến động số dư với id {{{place_id}}}|Tìm giao dịch với mã vùng/địa điểm cư trú. {{{place_id}}}|Hiển thị biến động số dư với id {{{place_id}}}|Tìm giao dịch của mã vùng/địa điểm cư trú. {{{place_id}}}|Liệt kê giao dịch có mã vùng/địa điểm cư trú. {{{place_id}}}|Tra cứu biến động số dư với id {{{place_id}}}|Liệt kê lệnh chuyển tiền với số {{{place_id}}}|Liệt kê history của mã {{{place_id}}}|Xem chi tiết history có mã vùng/địa điểm cư trú. {{{place_id}}}|Cho tôi xem lệnh chuyển tiền theo mã vùng/địa điểm cư trú. {{{place_id}}}</t>
-  </si>
-  <si>
-    <t>Kiểm tra biến động số dư theo ví dụ: ca tp. hà nội {{{place_of_issue}}}|Tra cứu giao dịch với ví dụ: ca tp. hà nội {{{place_of_issue}}}|Tìm lệnh chuyển tiền có ví dụ: ca tp. hà nội {{{place_of_issue}}}|Search lệnh chuyển tiền tại nơi cấp giấy tờ định danh {{{place_of_issue}}}|Tìm biến động số dư mang nơi cấp giấy tờ định danh {{{place_of_issue}}}|Search lệnh chuyển tiền với ví dụ: ca tp. hà nội {{{place_of_issue}}}|Tra cứu history mang ví dụ: ca tp. hà nội {{{place_of_issue}}}|Tìm lệnh chuyển tiền theo ví dụ: ca tp. hà nội {{{place_of_issue}}}|Cho tôi xem lệnh chuyển tiền với nơi cấp giấy tờ định danh {{{place_of_issue}}}|Liệt kê history với nơi cấp giấy tờ định danh {{{place_of_issue}}}|Hiển thị biến động số dư theo nơi cấp giấy tờ định danh {{{place_of_issue}}}|Hiển thị giao dịch mang ví dụ: ca tp. hà nội {{{place_of_issue}}}|Xem chi tiết lệnh chuyển tiền của ví dụ: ca tp. hà nội {{{place_of_issue}}}|Search biến động số dư với ví dụ: ca tp. hà nội {{{place_of_issue}}}|Cho tôi xem giao dịch tại nơi cấp giấy tờ định danh {{{place_of_issue}}}</t>
-  </si>
-  <si>
-    <t>Kiểm tra lệnh chuyển tiền với mã {{{unique_id}}}|Tra cứu biến động số dư có mã định danh duy nhất {{{unique_id}}}|Hiển thị lệnh chuyển tiền mang id {{{unique_id}}}|Search giao dịch của mã {{{unique_id}}}|Kiểm tra biến động số dư với id {{{unique_id}}}|Hiển thị biến động số dư với id {{{unique_id}}}|Tra cứu biến động số dư với id {{{unique_id}}}|Liệt kê lệnh chuyển tiền với số {{{unique_id}}}|Liệt kê history của mã {{{unique_id}}}|Tra cứu history mang thường đối soát liên hệ thống {{{unique_id}}}|Hiển thị lệnh chuyển tiền theo thường đối soát liên hệ thống {{{unique_id}}}|Liệt kê biến động số dư với thường đối soát liên hệ thống {{{unique_id}}}|Cho tôi xem giao dịch có số {{{unique_id}}}|Tra cứu biến động số dư với thường đối soát liên hệ thống {{{unique_id}}}|Kiểm tra biến động số dư tại mã {{{unique_id}}}</t>
-  </si>
-  <si>
-    <t>Tìm biến động số dư theo giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}|Kiểm tra history của giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}|Liệt kê biến động số dư theo giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}|Tìm biến động số dư với giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}|Cho tôi xem giao dịch có giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}|Tìm giao dịch với giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}|Tìm lệnh chuyển tiền mang giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}|Cho tôi xem giao dịch của giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}|Kiểm tra history có giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}|Kiểm tra history với giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}|Xem chi tiết biến động số dư theo giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}|Tra cứu history với giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}|Hiển thị lệnh chuyển tiền của giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}|Kiểm tra biến động số dư theo giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}|Tìm history tại giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}</t>
-  </si>
-  <si>
-    <t>Lọc các lệnh chuyển tiền theo trạng thái bản ghi {{{status}}}|Lọc các lệnh chuyển tiền với trạng thái {{{status}}}|Những history với ví dụ: 1-hiệu lực, 0-hết hiệu lực {{{status}}}|Các history của ví dụ: 1-hiệu lực, 0-hết hiệu lực {{{status}}}|Các biến động số dư tại tình trạng {{{status}}}|Những giao dịch theo kết quả {{{status}}}|Danh sách giao dịch tại ví dụ: 1-hiệu lực, 0-hết hiệu lực {{{status}}}|Các lệnh chuyển tiền theo tình trạng {{{status}}}|Những biến động số dư của trạng thái {{{status}}}|Danh sách history tại tình trạng {{{status}}}|Các history mang ví dụ: 1-hiệu lực, 0-hết hiệu lực {{{status}}}|Danh sách giao dịch có trạng thái {{{status}}}|Các history với trạng thái bản ghi {{{status}}}|Lọc các giao dịch với trạng thái {{{status}}}|Danh sách biến động số dư của kết quả {{{status}}}</t>
-  </si>
-  <si>
-    <t>Danh sách lệnh chuyển tiền tại trạng thái cũ khách hàng {{{old_customer_status}}}|Lọc các lệnh chuyển tiền với trạng thái {{{old_customer_status}}}|Những history theo trạng thái cũ khách hàng {{{old_customer_status}}}|Các biến động số dư tại tình trạng {{{old_customer_status}}}|Những giao dịch theo kết quả {{{old_customer_status}}}|Các lệnh chuyển tiền mang trạng thái cũ khách hàng {{{old_customer_status}}}|Các lệnh chuyển tiền theo tình trạng {{{old_customer_status}}}|Những biến động số dư của trạng thái {{{old_customer_status}}}|Danh sách giao dịch theo trạng thái cũ khách hàng {{{old_customer_status}}}|Danh sách history tại tình trạng {{{old_customer_status}}}|Các biến động số dư tại trạng thái cũ khách hàng {{{old_customer_status}}}|Danh sách giao dịch có trạng thái {{{old_customer_status}}}|Lọc các giao dịch với trạng thái {{{old_customer_status}}}|Danh sách biến động số dư của kết quả {{{old_customer_status}}}|Các biến động số dư với tình trạng {{{old_customer_status}}}</t>
-  </si>
-  <si>
-    <t>Lọc các lệnh chuyển tiền với trạng thái {{{new_customer_status}}}|Các history của sau khi cập nhật {{{new_customer_status}}}|Các history có trạng thái mới khách hàng {{{new_customer_status}}}|Các biến động số dư tại tình trạng {{{new_customer_status}}}|Những giao dịch theo kết quả {{{new_customer_status}}}|Danh sách giao dịch mang trạng thái mới khách hàng {{{new_customer_status}}}|Các lệnh chuyển tiền mang sau khi cập nhật {{{new_customer_status}}}|Các lệnh chuyển tiền theo tình trạng {{{new_customer_status}}}|Những biến động số dư của trạng thái {{{new_customer_status}}}|Danh sách history tại tình trạng {{{new_customer_status}}}|Lọc các giao dịch mang trạng thái mới khách hàng {{{new_customer_status}}}|Danh sách history tại trạng thái mới khách hàng {{{new_customer_status}}}|Danh sách giao dịch có trạng thái {{{new_customer_status}}}|Lọc các giao dịch với trạng thái {{{new_customer_status}}}|Danh sách biến động số dư của kết quả {{{new_customer_status}}}</t>
-  </si>
-  <si>
-    <t>Xem chi tiết giao dịch có đường dẫn ảnh mặt trước giấy tờ định danh {{{unique_image_front}}}|Search history có cmnd/cccd {{{unique_image_front}}}|Hiển thị history có đường dẫn ảnh mặt trước giấy tờ định danh {{{unique_image_front}}}|Cho tôi xem giao dịch của đường dẫn ảnh mặt trước giấy tờ định danh {{{unique_image_front}}}|Search giao dịch tại đường dẫn ảnh mặt trước giấy tờ định danh {{{unique_image_front}}}|Xem chi tiết history của cmnd/cccd {{{unique_image_front}}}|Hiển thị lệnh chuyển tiền có đường dẫn ảnh mặt trước giấy tờ định danh {{{unique_image_front}}}|Kiểm tra biến động số dư mang đường dẫn ảnh mặt trước giấy tờ định danh {{{unique_image_front}}}|Cho tôi xem giao dịch mang cmnd/cccd {{{unique_image_front}}}|Tra cứu giao dịch với đường dẫn ảnh mặt trước giấy tờ định danh {{{unique_image_front}}}|Xem chi tiết lệnh chuyển tiền tại đường dẫn ảnh mặt trước giấy tờ định danh {{{unique_image_front}}}|Kiểm tra lệnh chuyển tiền của đường dẫn ảnh mặt trước giấy tờ định danh {{{unique_image_front}}}|Tra cứu lệnh chuyển tiền tại cmnd/cccd {{{unique_image_front}}}|Tìm history của cmnd/cccd {{{unique_image_front}}}|Tìm biến động số dư tại cmnd/cccd {{{unique_image_front}}}</t>
-  </si>
-  <si>
-    <t>Cho tôi xem giao dịch mang đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}|Cho tôi xem history tại đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}|Liệt kê biến động số dư với đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}|Liệt kê history có đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}|Xem chi tiết history có đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}|Kiểm tra biến động số dư mang đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}|Search lệnh chuyển tiền có đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}|Xem chi tiết biến động số dư tại đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}|Tìm biến động số dư với đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}|Hiển thị giao dịch có đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}|Xem chi tiết lệnh chuyển tiền có đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}|Cho tôi xem biến động số dư có đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}|Tìm giao dịch tại đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}|Tìm history theo đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}|Hiển thị history có đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}</t>
+    <t>Xem chi tiết biến động số dư tại số {{{id}}}
+Xem chi tiết lệnh chuyển tiền theo id tự tăng, khóa chính {{{id}}}
+Tra cứu giao dịch tại mã {{{id}}}
+Kiểm tra biến động số dư có mã {{{id}}}
+Search biến động số dư theo primary key {{{id}}}
+Tra cứu giao dịch của số {{{id}}}
+Cho tôi xem giao dịch với id {{{id}}}
+Tra cứu biến động số dư theo số {{{id}}}
+Hiển thị giao dịch mang id {{{id}}}
+Tra cứu giao dịch tại số {{{id}}}
+Kiểm tra history với id tự tăng, khóa chính {{{id}}}
+Tìm biến động số dư với số {{{id}}}
+Liệt kê lệnh chuyển tiền của mã {{{id}}}
+mã {{{id}}} là bao nhiêu
+Kiểm tra lệnh chuyển tiền của primary key {{{id}}}</t>
+  </si>
+  <si>
+    <t>Cho tôi xem giao dịch với customer information file {{{cif_no}}}
+Liệt kê history của số cif {{{cif_no}}}
+Cho tôi xem giao dịch của customer information file {{{cif_no}}}
+Tìm history có customer information file {{{cif_no}}}
+Liệt kê biến động số dư theo số cif {{{cif_no}}}
+Tra cứu lệnh chuyển tiền với số cif {{{cif_no}}}
+Liệt kê lệnh chuyển tiền của số cif {{{cif_no}}}
+Tìm biến động số dư với customer information file {{{cif_no}}}
+Xem chi tiết history với customer information file {{{cif_no}}}
+Cho tôi xem history mang số cif {{{cif_no}}}
+Tìm giao dịch có customer information file {{{cif_no}}}
+Tra cứu history có số cif {{{cif_no}}}
+Kiểm tra history tại customer information file {{{cif_no}}}
+Xem chi tiết history mang số cif {{{cif_no}}}
+Search biến động số dư theo customer information file {{{cif_no}}}</t>
+  </si>
+  <si>
+    <t>Xem chi tiết biến động số dư tại số {{{customer_id}}}
+Tra cứu giao dịch tại mã {{{customer_id}}}
+Kiểm tra biến động số dư có mã {{{customer_id}}}
+Kiểm tra lệnh chuyển tiền của id định danh khách hàng nội bộ. {{{customer_id}}}
+Tra cứu giao dịch của số {{{customer_id}}}
+Cho tôi xem giao dịch với id {{{customer_id}}}
+Hiển thị lệnh chuyển tiền mang id định danh khách hàng nội bộ. {{{customer_id}}}
+Tra cứu biến động số dư theo số {{{customer_id}}}
+Hiển thị giao dịch mang id {{{customer_id}}}
+Tra cứu giao dịch tại số {{{customer_id}}}
+Xem chi tiết history có id định danh khách hàng nội bộ. {{{customer_id}}}
+Tìm biến động số dư với số {{{customer_id}}}
+Hiển thị lệnh chuyển tiền của id định danh khách hàng nội bộ. {{{customer_id}}}
+Liệt kê lệnh chuyển tiền của mã {{{customer_id}}}
+mã {{{customer_id}}} là bao nhiêu</t>
+  </si>
+  <si>
+    <t>Hiển thị history theo mã số khách hàng {{{customer_no}}}
+Cho tôi xem biến động số dư với có thể khác với cif tùy theo cấu trúc hệ thống {{{customer_no}}}
+Tìm giao dịch theo có thể khác với cif tùy theo cấu trúc hệ thống {{{customer_no}}}
+Tìm biến động số dư của mã số khách hàng {{{customer_no}}}
+Xem chi tiết biến động số dư có mã số khách hàng {{{customer_no}}}
+Xem chi tiết lệnh chuyển tiền tại mã số khách hàng {{{customer_no}}}
+Tìm history với mã số khách hàng {{{customer_no}}}
+Tìm lệnh chuyển tiền theo mã số khách hàng {{{customer_no}}}
+Tìm biến động số dư theo có thể khác với cif tùy theo cấu trúc hệ thống {{{customer_no}}}
+Kiểm tra history với mã số khách hàng {{{customer_no}}}
+Search biến động số dư tại có thể khác với cif tùy theo cấu trúc hệ thống {{{customer_no}}}
+Xem chi tiết lệnh chuyển tiền tại có thể khác với cif tùy theo cấu trúc hệ thống {{{customer_no}}}
+Liệt kê lệnh chuyển tiền mang có thể khác với cif tùy theo cấu trúc hệ thống {{{customer_no}}}
+Xem chi tiết lệnh chuyển tiền của có thể khác với cif tùy theo cấu trúc hệ thống {{{customer_no}}}
+Search giao dịch tại có thể khác với cif tùy theo cấu trúc hệ thống {{{customer_no}}}</t>
+  </si>
+  <si>
+    <t>Xem chi tiết giao dịch mang nếu dữ liệu được đẩy từ khác sang {{{system_id}}}
+Xem chi tiết biến động số dư tại số {{{system_id}}}
+Tra cứu giao dịch tại mã {{{system_id}}}
+Hiển thị biến động số dư theo nếu dữ liệu được đẩy từ khác sang {{{system_id}}}
+Kiểm tra biến động số dư có mã {{{system_id}}}
+Liệt kê lệnh chuyển tiền theo id nguồn {{{system_id}}}
+Tra cứu giao dịch của số {{{system_id}}}
+Tra cứu history mang nếu dữ liệu được đẩy từ khác sang {{{system_id}}}
+Cho tôi xem giao dịch với id {{{system_id}}}
+Tra cứu biến động số dư theo số {{{system_id}}}
+Hiển thị giao dịch mang id {{{system_id}}}
+Tra cứu giao dịch tại số {{{system_id}}}
+Cho tôi xem biến động số dư có nếu dữ liệu được đẩy từ khác sang {{{system_id}}}
+Hiển thị lệnh chuyển tiền có id nguồn {{{system_id}}}
+Tìm biến động số dư với số {{{system_id}}}</t>
+  </si>
+  <si>
+    <t>Liệt kê biến động số dư mang chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
+Kiểm tra lệnh chuyển tiền mang chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
+Tra cứu history có chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
+Xem chi tiết giao dịch có chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
+Xem chi tiết history có chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
+Kiểm tra biến động số dư tại chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
+Search history theo chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
+Tra cứu biến động số dư của chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
+Kiểm tra biến động số dư của chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
+Tra cứu giao dịch mang chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
+Xem chi tiết giao dịch tại chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
+Liệt kê history với chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
+Cho tôi xem biến động số dư của chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
+Tìm history mang chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
+Kiểm tra biến động số dư với chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}</t>
+  </si>
+  <si>
+    <t>Các giao dịch của hình thức {{{cif_type}}}
+Những lệnh chuyển tiền tại loại cif {{{cif_type}}}
+Các lệnh chuyển tiền theo hình thức {{{cif_type}}}
+Những history tại ví dụ: cá nhân, doanh nghiệp, khách hàng ưu tiên... {{{cif_type}}}
+Các lệnh chuyển tiền tại hình thức {{{cif_type}}}
+Các history mang loại cif {{{cif_type}}}
+Các giao dịch mang loại {{{cif_type}}}
+Những history theo ví dụ: cá nhân, doanh nghiệp, khách hàng ưu tiên... {{{cif_type}}}
+Danh sách lệnh chuyển tiền theo ví dụ: cá nhân, doanh nghiệp, khách hàng ưu tiên... {{{cif_type}}}
+Các giao dịch tại loại {{{cif_type}}}
+Những giao dịch mang loại {{{cif_type}}}
+Lọc các biến động số dư của loại {{{cif_type}}}
+Những giao dịch có ví dụ: cá nhân, doanh nghiệp, khách hàng ưu tiên... {{{cif_type}}}
+Những giao dịch của loại cif {{{cif_type}}}
+Lọc các giao dịch mang loại {{{cif_type}}}</t>
+  </si>
+  <si>
+    <t>Tra cứu lệnh chuyển tiền tại mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
+Hiển thị lệnh chuyển tiền của mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
+Cho tôi xem lệnh chuyển tiền tại mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
+Tra cứu lệnh chuyển tiền theo mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
+Kiểm tra biến động số dư theo mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
+Tìm lệnh chuyển tiền của mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
+Hiển thị history mang mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
+Tra cứu history tại mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
+Cho tôi xem lệnh chuyển tiền theo mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
+Tìm history với mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
+Xem chi tiết biến động số dư với mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
+Liệt kê lệnh chuyển tiền mang mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
+Cho tôi xem giao dịch mang mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
+Cho tôi xem history của mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
+Search biến động số dư theo mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}</t>
+  </si>
+  <si>
+    <t>Những lệnh chuyển tiền mang kết quả {{{customer_status}}}
+Lọc các biến động số dư của trạng thái {{{customer_status}}}
+Các giao dịch mang trạng thái hiện tại khách hàng {{{customer_status}}}
+Lọc các lệnh chuyển tiền mang kết quả {{{customer_status}}}
+Các lệnh chuyển tiền tại trạng thái hiện tại khách hàng {{{customer_status}}}
+Những biến động số dư theo tình trạng {{{customer_status}}}
+Danh sách history của trạng thái hiện tại khách hàng {{{customer_status}}}
+Các history tại active, inactive, closed... {{{customer_status}}}
+Danh sách biến động số dư của trạng thái {{{customer_status}}}
+Những giao dịch của kết quả {{{customer_status}}}
+Danh sách giao dịch theo kết quả {{{customer_status}}}
+Các lệnh chuyển tiền của tình trạng {{{customer_status}}}
+Danh sách history với trạng thái hiện tại khách hàng {{{customer_status}}}
+Danh sách giao dịch mang trạng thái hiện tại khách hàng {{{customer_status}}}
+Các giao dịch mang tình trạng {{{customer_status}}}</t>
+  </si>
+  <si>
+    <t>Hiển thị biến động số dư theo ngày cấp giấy tờ định danh {{{date_of_issue}}}
+Tìm giao dịch theo ngày cấp giấy tờ định danh {{{date_of_issue}}}
+Kiểm tra history mang ngày cấp giấy tờ định danh {{{date_of_issue}}}
+Search lệnh chuyển tiền tại cmnd/cccd/hộ chiếu {{{date_of_issue}}}
+Tìm lệnh chuyển tiền mang ngày cấp giấy tờ định danh {{{date_of_issue}}}
+Xem chi tiết biến động số dư mang cmnd/cccd/hộ chiếu {{{date_of_issue}}}
+Xem chi tiết biến động số dư tại cmnd/cccd/hộ chiếu {{{date_of_issue}}}
+Liệt kê lệnh chuyển tiền theo ngày cấp giấy tờ định danh {{{date_of_issue}}}
+Xem chi tiết lệnh chuyển tiền của ngày cấp giấy tờ định danh {{{date_of_issue}}}
+Liệt kê lệnh chuyển tiền của cmnd/cccd/hộ chiếu {{{date_of_issue}}}
+Liệt kê giao dịch mang cmnd/cccd/hộ chiếu {{{date_of_issue}}}
+Kiểm tra lệnh chuyển tiền với ngày cấp giấy tờ định danh {{{date_of_issue}}}
+Liệt kê history theo ngày cấp giấy tờ định danh {{{date_of_issue}}}
+Hiển thị history của ngày cấp giấy tờ định danh {{{date_of_issue}}}
+Xem chi tiết biến động số dư mang ngày cấp giấy tờ định danh {{{date_of_issue}}}</t>
+  </si>
+  <si>
+    <t>Xem chi tiết biến động số dư tại số {{{identify_id}}}
+Tra cứu giao dịch tại mã {{{identify_id}}}
+Kiểm tra biến động số dư có mã {{{identify_id}}}
+Tìm lệnh chuyển tiền tại số cmnd, cccd hoặc hộ chiếu {{{identify_id}}}
+Tra cứu giao dịch của số {{{identify_id}}}
+Cho tôi xem giao dịch với id {{{identify_id}}}
+Tra cứu biến động số dư theo số {{{identify_id}}}
+Hiển thị giao dịch mang id {{{identify_id}}}
+Tra cứu giao dịch tại số {{{identify_id}}}
+Search lệnh chuyển tiền với số cmnd, cccd hoặc hộ chiếu {{{identify_id}}}
+Tìm biến động số dư với số {{{identify_id}}}
+Hiển thị biến động số dư mang số giấy tờ định danh {{{identify_id}}}
+Cho tôi xem history có số cmnd, cccd hoặc hộ chiếu {{{identify_id}}}
+Liệt kê lệnh chuyển tiền của mã {{{identify_id}}}
+mã {{{identify_id}}} là bao nhiêu</t>
+  </si>
+  <si>
+    <t>Xem chi tiết biến động số dư tại số {{{identify_level}}}
+Tra cứu giao dịch tại mã {{{identify_level}}}
+Tra cứu giao dịch có cấp độ định danh {{{identify_level}}}
+Tra cứu lệnh chuyển tiền theo cấp độ định danh {{{identify_level}}}
+Kiểm tra biến động số dư có mã {{{identify_level}}}
+Tra cứu giao dịch của số {{{identify_level}}}
+Cho tôi xem giao dịch với id {{{identify_level}}}
+Tra cứu biến động số dư theo số {{{identify_level}}}
+Tìm giao dịch tại cấp độ định danh {{{identify_level}}}
+Tra cứu giao dịch tại số {{{identify_level}}}
+Hiển thị giao dịch mang id {{{identify_level}}}
+Tìm lệnh chuyển tiền có cấp độ định danh {{{identify_level}}}
+Cho tôi xem history với cấp độ định danh {{{identify_level}}}
+Tìm biến động số dư với số {{{identify_level}}}
+Hiển thị biến động số dư với ví dụ: đã xác thực - ekyc, chưa xác thực {{{identify_level}}}</t>
+  </si>
+  <si>
+    <t>Xem chi tiết biến động số dư tại số {{{identify_name}}}
+Tra cứu giao dịch tại mã {{{identify_name}}}
+Hiển thị history có ví dụ: "identity card", "passport" {{{identify_name}}}
+Cho tôi xem biến động số dư của ví dụ: "identity card", "passport" {{{identify_name}}}
+Kiểm tra biến động số dư có mã {{{identify_name}}}
+Tra cứu giao dịch của số {{{identify_name}}}
+Cho tôi xem giao dịch với id {{{identify_name}}}
+Tra cứu biến động số dư theo số {{{identify_name}}}
+Xem chi tiết lệnh chuyển tiền mang ví dụ: "identity card", "passport" {{{identify_name}}}
+Hiển thị giao dịch mang id {{{identify_name}}}
+Tra cứu giao dịch tại số {{{identify_name}}}
+Liệt kê lệnh chuyển tiền mang loại giấy tờ định danh {{{identify_name}}}
+Tìm biến động số dư với số {{{identify_name}}}
+Liệt kê lệnh chuyển tiền của mã {{{identify_name}}}
+Search giao dịch theo ví dụ: "identity card", "passport" {{{identify_name}}}</t>
+  </si>
+  <si>
+    <t>Sao kê giao dịch từ ngày {{start_date}} đến {{end_date}}
+Liệt kê lịch sử trong khoảng thời gian {{start_date}} - {{end_date}}
+Kiểm tra giao dịch phát sinh từ {{start_date}} tới {{end_date}}
+Cho tôi xem biến động số dư giữa {{start_date}} và {{end_date}}</t>
+  </si>
+  <si>
+    <t>Tính tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. của các giao dịch có cif_type là {{cif_type}}
+Xem tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. theo cif_type {{cif_type}}
+Tính tổng phí của các giao dịch có cif_type là {{cif_type}}
+Xem tổng phí theo cif_type {{cif_type}}
+Tính tổng tiền phí của các giao dịch có cif_type là {{cif_type}}
+Xem tổng tiền phí theo cif_type {{cif_type}}
+Tổng cộng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. của các giao dịch có cif_type là {{cif_type}}
+Xem tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. theo cif_type {{cif_type}}
+Tổng cộng phí của các giao dịch có cif_type là {{cif_type}}
+Xem tổng phí theo cif_type {{cif_type}}
+Tổng cộng tiền phí của các giao dịch có cif_type là {{cif_type}}
+Xem tổng tiền phí theo cif_type {{cif_type}}
+Thống kê đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. của các giao dịch có cif_type là {{cif_type}}
+Xem tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. theo cif_type {{cif_type}}
+Thống kê phí của các giao dịch có cif_type là {{cif_type}}
+Xem tổng phí theo cif_type {{cif_type}}
+Thống kê tiền phí của các giao dịch có cif_type là {{cif_type}}
+Xem tổng tiền phí theo cif_type {{cif_type}}
+Cộng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. của các giao dịch có cif_type là {{cif_type}}
+Xem tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. theo cif_type {{cif_type}}
+Cộng phí của các giao dịch có cif_type là {{cif_type}}
+Xem tổng phí theo cif_type {{cif_type}}
+Cộng tiền phí của các giao dịch có cif_type là {{cif_type}}
+Xem tổng tiền phí theo cif_type {{cif_type}}
+Xem tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. của các giao dịch có cif_type là {{cif_type}}
+Xem tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. theo cif_type {{cif_type}}
+Xem tổng phí của các giao dịch có cif_type là {{cif_type}}
+Xem tổng phí theo cif_type {{cif_type}}
+Xem tổng tiền phí của các giao dịch có cif_type là {{cif_type}}
+Xem tổng tiền phí theo cif_type {{cif_type}}</t>
+  </si>
+  <si>
+    <t>Xem chi tiết biến động số dư tại số {{{nationality_id}}}
+Tra cứu giao dịch tại mã {{{nationality_id}}}
+Kiểm tra biến động số dư có mã {{{nationality_id}}}
+Tra cứu giao dịch của số {{{nationality_id}}}
+Cho tôi xem giao dịch với id {{{nationality_id}}}
+Tra cứu biến động số dư theo số {{{nationality_id}}}
+Kiểm tra lệnh chuyển tiền có ví dụ: vn, us, jp {{{nationality_id}}}
+Hiển thị giao dịch mang id {{{nationality_id}}}
+Tra cứu giao dịch tại số {{{nationality_id}}}
+Tra cứu biến động số dư của ví dụ: vn, us, jp {{{nationality_id}}}
+Search biến động số dư theo mã quốc tịch {{{nationality_id}}}
+Tìm giao dịch của ví dụ: vn, us, jp {{{nationality_id}}}
+Kiểm tra history mang ví dụ: vn, us, jp {{{nationality_id}}}
+Tìm biến động số dư với số {{{nationality_id}}}
+Liệt kê lệnh chuyển tiền của mã {{{nationality_id}}}</t>
+  </si>
+  <si>
+    <t>Xem chi tiết biến động số dư tại số {{{place_id}}}
+Tra cứu giao dịch tại mã {{{place_id}}}
+Kiểm tra biến động số dư có mã {{{place_id}}}
+Tra cứu giao dịch của số {{{place_id}}}
+Cho tôi xem giao dịch với id {{{place_id}}}
+Liệt kê giao dịch với mã vùng/địa điểm cư trú. {{{place_id}}}
+Tra cứu biến động số dư theo số {{{place_id}}}
+Hiển thị giao dịch mang id {{{place_id}}}
+Tra cứu giao dịch tại số {{{place_id}}}
+Search biến động số dư tại mã vùng/địa điểm cư trú. {{{place_id}}}
+Tìm biến động số dư với số {{{place_id}}}
+Liệt kê lệnh chuyển tiền của mã {{{place_id}}}
+mã {{{place_id}}} là bao nhiêu
+Tra cứu history theo mã vùng/địa điểm cư trú. {{{place_id}}}
+Tra cứu lệnh chuyển tiền tại mã {{{place_id}}}</t>
+  </si>
+  <si>
+    <t>Cho tôi xem giao dịch theo ví dụ: ca tp. hà nội {{{place_of_issue}}}
+Liệt kê lệnh chuyển tiền mang ví dụ: ca tp. hà nội {{{place_of_issue}}}
+Liệt kê history tại nơi cấp giấy tờ định danh {{{place_of_issue}}}
+Cho tôi xem biến động số dư theo ví dụ: ca tp. hà nội {{{place_of_issue}}}
+Search history mang nơi cấp giấy tờ định danh {{{place_of_issue}}}
+Tìm lệnh chuyển tiền theo nơi cấp giấy tờ định danh {{{place_of_issue}}}
+Cho tôi xem history mang ví dụ: ca tp. hà nội {{{place_of_issue}}}
+Xem chi tiết biến động số dư tại ví dụ: ca tp. hà nội {{{place_of_issue}}}
+Xem chi tiết giao dịch mang nơi cấp giấy tờ định danh {{{place_of_issue}}}
+Cho tôi xem history có ví dụ: ca tp. hà nội {{{place_of_issue}}}
+Cho tôi xem giao dịch của ví dụ: ca tp. hà nội {{{place_of_issue}}}
+Kiểm tra history theo ví dụ: ca tp. hà nội {{{place_of_issue}}}
+Kiểm tra history của ví dụ: ca tp. hà nội {{{place_of_issue}}}
+Liệt kê lệnh chuyển tiền của nơi cấp giấy tờ định danh {{{place_of_issue}}}
+Tìm giao dịch với ví dụ: ca tp. hà nội {{{place_of_issue}}}</t>
+  </si>
+  <si>
+    <t>Xem chi tiết biến động số dư tại số {{{unique_id}}}
+Tra cứu giao dịch tại mã {{{unique_id}}}
+Kiểm tra biến động số dư có mã {{{unique_id}}}
+Tìm history theo mã định danh duy nhất {{{unique_id}}}
+Tra cứu giao dịch của số {{{unique_id}}}
+Cho tôi xem giao dịch với id {{{unique_id}}}
+Tra cứu biến động số dư theo số {{{unique_id}}}
+Tìm giao dịch với thường đối soát liên hệ thống {{{unique_id}}}
+Tra cứu giao dịch tại số {{{unique_id}}}
+Hiển thị giao dịch mang id {{{unique_id}}}
+Cho tôi xem biến động số dư với thường đối soát liên hệ thống {{{unique_id}}}
+Tìm biến động số dư với số {{{unique_id}}}
+Liệt kê lệnh chuyển tiền của mã {{{unique_id}}}
+Liệt kê biến động số dư mang mã định danh duy nhất {{{unique_id}}}
+mã {{{unique_id}}} là bao nhiêu</t>
+  </si>
+  <si>
+    <t>Tìm giao dịch theo giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
+Xem chi tiết giao dịch của giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
+Kiểm tra lệnh chuyển tiền theo giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
+Hiển thị lệnh chuyển tiền mang giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
+Tìm history của giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
+Tra cứu biến động số dư mang giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
+Cho tôi xem lệnh chuyển tiền theo giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
+Cho tôi xem history với giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
+Cho tôi xem giao dịch tại giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
+Xem chi tiết lệnh chuyển tiền của giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
+Liệt kê giao dịch tại giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
+Tra cứu giao dịch mang giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
+Kiểm tra history theo giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
+Hiển thị lệnh chuyển tiền theo giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
+Xem chi tiết lệnh chuyển tiền có giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}</t>
+  </si>
+  <si>
+    <t>Những lệnh chuyển tiền mang kết quả {{{status}}}
+Lọc các biến động số dư của trạng thái {{{status}}}
+Lọc các lệnh chuyển tiền mang kết quả {{{status}}}
+Danh sách lệnh chuyển tiền có trạng thái bản ghi {{{status}}}
+Lọc các lệnh chuyển tiền theo ví dụ: 1-hiệu lực, 0-hết hiệu lực {{{status}}}
+Các biến động số dư theo trạng thái bản ghi {{{status}}}
+Các lệnh chuyển tiền có trạng thái bản ghi {{{status}}}
+Những biến động số dư theo tình trạng {{{status}}}
+Lọc các history của trạng thái bản ghi {{{status}}}
+Các lệnh chuyển tiền của trạng thái bản ghi {{{status}}}
+Các lệnh chuyển tiền mang trạng thái bản ghi {{{status}}}
+Danh sách biến động số dư của trạng thái {{{status}}}
+Những giao dịch của kết quả {{{status}}}
+Lọc các biến động số dư của trạng thái bản ghi {{{status}}}
+Danh sách giao dịch theo kết quả {{{status}}}</t>
+  </si>
+  <si>
+    <t>Những lệnh chuyển tiền mang kết quả {{{old_customer_status}}}
+Lọc các biến động số dư của trạng thái {{{old_customer_status}}}
+Những lệnh chuyển tiền tại trước khi thay đổi {{{old_customer_status}}}
+Danh sách lệnh chuyển tiền theo trước khi thay đổi {{{old_customer_status}}}
+Danh sách lệnh chuyển tiền tại trước khi thay đổi {{{old_customer_status}}}
+Lọc các giao dịch tại trạng thái cũ khách hàng {{{old_customer_status}}}
+Danh sách giao dịch theo trước khi thay đổi {{{old_customer_status}}}
+Lọc các lệnh chuyển tiền mang kết quả {{{old_customer_status}}}
+Danh sách biến động số dư theo trạng thái cũ khách hàng {{{old_customer_status}}}
+Những biến động số dư theo tình trạng {{{old_customer_status}}}
+Lọc các biến động số dư mang trước khi thay đổi {{{old_customer_status}}}
+Danh sách history với trước khi thay đổi {{{old_customer_status}}}
+Danh sách biến động số dư của trạng thái {{{old_customer_status}}}
+Những giao dịch của kết quả {{{old_customer_status}}}
+Những giao dịch có trạng thái cũ khách hàng {{{old_customer_status}}}</t>
+  </si>
+  <si>
+    <t>Các history có sau khi cập nhật {{{new_customer_status}}}
+Những lệnh chuyển tiền mang kết quả {{{new_customer_status}}}
+Lọc các biến động số dư của trạng thái {{{new_customer_status}}}
+Lọc các giao dịch mang trạng thái mới khách hàng {{{new_customer_status}}}
+Lọc các biến động số dư có trạng thái mới khách hàng {{{new_customer_status}}}
+Lọc các lệnh chuyển tiền mang kết quả {{{new_customer_status}}}
+Các giao dịch mang trạng thái mới khách hàng {{{new_customer_status}}}
+Những biến động số dư theo tình trạng {{{new_customer_status}}}
+Lọc các giao dịch với sau khi cập nhật {{{new_customer_status}}}
+Danh sách lệnh chuyển tiền có sau khi cập nhật {{{new_customer_status}}}
+Danh sách biến động số dư của trạng thái {{{new_customer_status}}}
+Những giao dịch của kết quả {{{new_customer_status}}}
+Danh sách biến động số dư mang trạng thái mới khách hàng {{{new_customer_status}}}
+Danh sách giao dịch theo kết quả {{{new_customer_status}}}
+Những biến động số dư của sau khi cập nhật {{{new_customer_status}}}</t>
+  </si>
+  <si>
+    <t>Hiển thị lệnh chuyển tiền tại cmnd/cccd {{{unique_image_front}}}
+Hiển thị lệnh chuyển tiền theo đường dẫn ảnh mặt trước giấy tờ định danh {{{unique_image_front}}}
+Liệt kê giao dịch có đường dẫn ảnh mặt trước giấy tờ định danh {{{unique_image_front}}}
+Kiểm tra biến động số dư với cmnd/cccd {{{unique_image_front}}}
+Hiển thị lệnh chuyển tiền theo cmnd/cccd {{{unique_image_front}}}
+Tìm lệnh chuyển tiền của cmnd/cccd {{{unique_image_front}}}
+Cho tôi xem lệnh chuyển tiền tại cmnd/cccd {{{unique_image_front}}}
+đường dẫn ảnh mặt trước giấy tờ định danh {{{unique_image_front}}} là bao nhiêu
+Search lệnh chuyển tiền theo đường dẫn ảnh mặt trước giấy tờ định danh {{{unique_image_front}}}
+Tra cứu giao dịch theo cmnd/cccd {{{unique_image_front}}}
+Tìm biến động số dư theo cmnd/cccd {{{unique_image_front}}}
+Hiển thị lệnh chuyển tiền có đường dẫn ảnh mặt trước giấy tờ định danh {{{unique_image_front}}}
+Xem chi tiết biến động số dư với đường dẫn ảnh mặt trước giấy tờ định danh {{{unique_image_front}}}
+Hiển thị giao dịch mang đường dẫn ảnh mặt trước giấy tờ định danh {{{unique_image_front}}}
+Cho tôi xem biến động số dư có đường dẫn ảnh mặt trước giấy tờ định danh {{{unique_image_front}}}</t>
+  </si>
+  <si>
+    <t>Hiển thị lệnh chuyển tiền mang đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
+Xem chi tiết giao dịch theo đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
+Kiểm tra history mang đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
+Liệt kê giao dịch theo đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
+Cho tôi xem lệnh chuyển tiền có đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
+Cho tôi xem history của đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
+Liệt kê history mang đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
+Search giao dịch mang đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
+Search history tại đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
+Tra cứu biến động số dư mang đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
+Tra cứu lệnh chuyển tiền theo đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
+Liệt kê biến động số dư có đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
+Tra cứu history tại đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
+Tìm giao dịch theo đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
+Cho tôi xem lệnh chuyển tiền mang đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}</t>
   </si>
   <si>
     <t>id, tra cứu, tìm kiếm</t>

--- a/Text2SQL_Template/output/ddq_autogen_customer.xlsx
+++ b/Text2SQL_Template/output/ddq_autogen_customer.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="133">
   <si>
     <t>document</t>
   </si>
@@ -31,661 +31,502 @@
     <t>metadata</t>
   </si>
   <si>
-    <t>Tra cứu customer theo id</t>
-  </si>
-  <si>
-    <t>Tra cứu customer theo cif_no</t>
-  </si>
-  <si>
-    <t>Tra cứu customer theo customer_id</t>
-  </si>
-  <si>
-    <t>Tra cứu customer theo customer_no</t>
-  </si>
-  <si>
-    <t>Tra cứu customer theo system_id</t>
-  </si>
-  <si>
-    <t>Tra cứu customer theo cif_branch</t>
-  </si>
-  <si>
-    <t>Lọc customer theo cif_type</t>
-  </si>
-  <si>
-    <t>Tra cứu customer theo branch_code</t>
-  </si>
-  <si>
-    <t>Lọc customer theo customer_status</t>
-  </si>
-  <si>
-    <t>Tra cứu customer theo date_of_issue</t>
-  </si>
-  <si>
-    <t>Tra cứu customer theo identify_id</t>
-  </si>
-  <si>
-    <t>Tra cứu customer theo identify_level</t>
-  </si>
-  <si>
-    <t>Tra cứu customer theo identify_name</t>
-  </si>
-  <si>
-    <t>Tra cứu customer theo khoảng thời gian (init_date)</t>
-  </si>
-  <si>
-    <t>Thống kê tổng is_fee_default theo cif_type</t>
-  </si>
-  <si>
-    <t>Tra cứu customer theo nationality_id</t>
-  </si>
-  <si>
-    <t>Tra cứu customer theo place_id</t>
-  </si>
-  <si>
-    <t>Tra cứu customer theo place_of_issue</t>
-  </si>
-  <si>
-    <t>Tra cứu customer theo unique_id</t>
-  </si>
-  <si>
-    <t>Tra cứu customer theo unique_value</t>
-  </si>
-  <si>
-    <t>Lọc customer theo status</t>
-  </si>
-  <si>
-    <t>Tra cứu customer theo khoảng thời gian (date_of_birth)</t>
-  </si>
-  <si>
-    <t>Lọc customer theo old_customer_status</t>
-  </si>
-  <si>
-    <t>Lọc customer theo new_customer_status</t>
-  </si>
-  <si>
-    <t>Tra cứu customer theo unique_image_front</t>
-  </si>
-  <si>
-    <t>Tra cứu customer theo unique_image_back</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác bản ghi dựa trên id</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác bản ghi dựa trên cif_no</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác bản ghi dựa trên customer_id</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác bản ghi dựa trên customer_no</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác bản ghi dựa trên system_id</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác bản ghi dựa trên cif_branch</t>
-  </si>
-  <si>
-    <t>Liệt kê danh sách theo tiêu chí cif_type</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác bản ghi dựa trên branch_code</t>
-  </si>
-  <si>
-    <t>Liệt kê danh sách theo tiêu chí customer_status</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác bản ghi dựa trên date_of_issue</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác bản ghi dựa trên identify_id</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác bản ghi dựa trên identify_level</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác bản ghi dựa trên identify_name</t>
-  </si>
-  <si>
-    <t>Lọc dữ liệu phát sinh trong một khoảng ngày giờ</t>
-  </si>
-  <si>
-    <t>Tính tổng giá trị is_fee_default được gom nhóm bởi cif_type</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác bản ghi dựa trên nationality_id</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác bản ghi dựa trên place_id</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác bản ghi dựa trên place_of_issue</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác bản ghi dựa trên unique_id</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác bản ghi dựa trên unique_value</t>
-  </si>
-  <si>
-    <t>Liệt kê danh sách theo tiêu chí status</t>
-  </si>
-  <si>
-    <t>Liệt kê danh sách theo tiêu chí old_customer_status</t>
-  </si>
-  <si>
-    <t>Liệt kê danh sách theo tiêu chí new_customer_status</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác bản ghi dựa trên unique_image_front</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác bản ghi dựa trên unique_image_back</t>
-  </si>
-  <si>
-    <t>Xem chi tiết biến động số dư tại số {{{id}}}
-Xem chi tiết lệnh chuyển tiền theo id tự tăng, khóa chính {{{id}}}
-Tra cứu giao dịch tại mã {{{id}}}
-Kiểm tra biến động số dư có mã {{{id}}}
-Search biến động số dư theo primary key {{{id}}}
-Tra cứu giao dịch của số {{{id}}}
-Cho tôi xem giao dịch với id {{{id}}}
-Tra cứu biến động số dư theo số {{{id}}}
-Hiển thị giao dịch mang id {{{id}}}
-Tra cứu giao dịch tại số {{{id}}}
-Kiểm tra history với id tự tăng, khóa chính {{{id}}}
-Tìm biến động số dư với số {{{id}}}
-Liệt kê lệnh chuyển tiền của mã {{{id}}}
-mã {{{id}}} là bao nhiêu
-Kiểm tra lệnh chuyển tiền của primary key {{{id}}}</t>
-  </si>
-  <si>
-    <t>Cho tôi xem giao dịch với customer information file {{{cif_no}}}
-Liệt kê history của số cif {{{cif_no}}}
-Cho tôi xem giao dịch của customer information file {{{cif_no}}}
-Tìm history có customer information file {{{cif_no}}}
-Liệt kê biến động số dư theo số cif {{{cif_no}}}
-Tra cứu lệnh chuyển tiền với số cif {{{cif_no}}}
-Liệt kê lệnh chuyển tiền của số cif {{{cif_no}}}
-Tìm biến động số dư với customer information file {{{cif_no}}}
-Xem chi tiết history với customer information file {{{cif_no}}}
-Cho tôi xem history mang số cif {{{cif_no}}}
-Tìm giao dịch có customer information file {{{cif_no}}}
-Tra cứu history có số cif {{{cif_no}}}
-Kiểm tra history tại customer information file {{{cif_no}}}
-Xem chi tiết history mang số cif {{{cif_no}}}
-Search biến động số dư theo customer information file {{{cif_no}}}</t>
-  </si>
-  <si>
-    <t>Xem chi tiết biến động số dư tại số {{{customer_id}}}
-Tra cứu giao dịch tại mã {{{customer_id}}}
-Kiểm tra biến động số dư có mã {{{customer_id}}}
-Kiểm tra lệnh chuyển tiền của id định danh khách hàng nội bộ. {{{customer_id}}}
-Tra cứu giao dịch của số {{{customer_id}}}
-Cho tôi xem giao dịch với id {{{customer_id}}}
-Hiển thị lệnh chuyển tiền mang id định danh khách hàng nội bộ. {{{customer_id}}}
-Tra cứu biến động số dư theo số {{{customer_id}}}
-Hiển thị giao dịch mang id {{{customer_id}}}
-Tra cứu giao dịch tại số {{{customer_id}}}
-Xem chi tiết history có id định danh khách hàng nội bộ. {{{customer_id}}}
-Tìm biến động số dư với số {{{customer_id}}}
-Hiển thị lệnh chuyển tiền của id định danh khách hàng nội bộ. {{{customer_id}}}
-Liệt kê lệnh chuyển tiền của mã {{{customer_id}}}
-mã {{{customer_id}}} là bao nhiêu</t>
-  </si>
-  <si>
-    <t>Hiển thị history theo mã số khách hàng {{{customer_no}}}
-Cho tôi xem biến động số dư với có thể khác với cif tùy theo cấu trúc hệ thống {{{customer_no}}}
-Tìm giao dịch theo có thể khác với cif tùy theo cấu trúc hệ thống {{{customer_no}}}
-Tìm biến động số dư của mã số khách hàng {{{customer_no}}}
-Xem chi tiết biến động số dư có mã số khách hàng {{{customer_no}}}
-Xem chi tiết lệnh chuyển tiền tại mã số khách hàng {{{customer_no}}}
-Tìm history với mã số khách hàng {{{customer_no}}}
-Tìm lệnh chuyển tiền theo mã số khách hàng {{{customer_no}}}
-Tìm biến động số dư theo có thể khác với cif tùy theo cấu trúc hệ thống {{{customer_no}}}
-Kiểm tra history với mã số khách hàng {{{customer_no}}}
-Search biến động số dư tại có thể khác với cif tùy theo cấu trúc hệ thống {{{customer_no}}}
-Xem chi tiết lệnh chuyển tiền tại có thể khác với cif tùy theo cấu trúc hệ thống {{{customer_no}}}
-Liệt kê lệnh chuyển tiền mang có thể khác với cif tùy theo cấu trúc hệ thống {{{customer_no}}}
-Xem chi tiết lệnh chuyển tiền của có thể khác với cif tùy theo cấu trúc hệ thống {{{customer_no}}}
-Search giao dịch tại có thể khác với cif tùy theo cấu trúc hệ thống {{{customer_no}}}</t>
-  </si>
-  <si>
-    <t>Xem chi tiết giao dịch mang nếu dữ liệu được đẩy từ khác sang {{{system_id}}}
-Xem chi tiết biến động số dư tại số {{{system_id}}}
-Tra cứu giao dịch tại mã {{{system_id}}}
-Hiển thị biến động số dư theo nếu dữ liệu được đẩy từ khác sang {{{system_id}}}
-Kiểm tra biến động số dư có mã {{{system_id}}}
-Liệt kê lệnh chuyển tiền theo id nguồn {{{system_id}}}
-Tra cứu giao dịch của số {{{system_id}}}
-Tra cứu history mang nếu dữ liệu được đẩy từ khác sang {{{system_id}}}
-Cho tôi xem giao dịch với id {{{system_id}}}
-Tra cứu biến động số dư theo số {{{system_id}}}
-Hiển thị giao dịch mang id {{{system_id}}}
-Tra cứu giao dịch tại số {{{system_id}}}
-Cho tôi xem biến động số dư có nếu dữ liệu được đẩy từ khác sang {{{system_id}}}
-Hiển thị lệnh chuyển tiền có id nguồn {{{system_id}}}
-Tìm biến động số dư với số {{{system_id}}}</t>
-  </si>
-  <si>
-    <t>Liệt kê biến động số dư mang chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
-Kiểm tra lệnh chuyển tiền mang chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
-Tra cứu history có chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
-Xem chi tiết giao dịch có chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
-Xem chi tiết history có chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
-Kiểm tra biến động số dư tại chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
-Search history theo chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
-Tra cứu biến động số dư của chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
-Kiểm tra biến động số dư của chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
-Tra cứu giao dịch mang chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
-Xem chi tiết giao dịch tại chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
-Liệt kê history với chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
-Cho tôi xem biến động số dư của chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
-Tìm history mang chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}
-Kiểm tra biến động số dư với chi nhánh nơi mở/quản lý mã cif này. {{{cif_branch}}}</t>
-  </si>
-  <si>
-    <t>Các giao dịch của hình thức {{{cif_type}}}
-Những lệnh chuyển tiền tại loại cif {{{cif_type}}}
-Các lệnh chuyển tiền theo hình thức {{{cif_type}}}
-Những history tại ví dụ: cá nhân, doanh nghiệp, khách hàng ưu tiên... {{{cif_type}}}
-Các lệnh chuyển tiền tại hình thức {{{cif_type}}}
-Các history mang loại cif {{{cif_type}}}
-Các giao dịch mang loại {{{cif_type}}}
-Những history theo ví dụ: cá nhân, doanh nghiệp, khách hàng ưu tiên... {{{cif_type}}}
-Danh sách lệnh chuyển tiền theo ví dụ: cá nhân, doanh nghiệp, khách hàng ưu tiên... {{{cif_type}}}
-Các giao dịch tại loại {{{cif_type}}}
-Những giao dịch mang loại {{{cif_type}}}
-Lọc các biến động số dư của loại {{{cif_type}}}
-Những giao dịch có ví dụ: cá nhân, doanh nghiệp, khách hàng ưu tiên... {{{cif_type}}}
-Những giao dịch của loại cif {{{cif_type}}}
-Lọc các giao dịch mang loại {{{cif_type}}}</t>
-  </si>
-  <si>
-    <t>Tra cứu lệnh chuyển tiền tại mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
-Hiển thị lệnh chuyển tiền của mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
-Cho tôi xem lệnh chuyển tiền tại mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
-Tra cứu lệnh chuyển tiền theo mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
-Kiểm tra biến động số dư theo mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
-Tìm lệnh chuyển tiền của mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
-Hiển thị history mang mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
-Tra cứu history tại mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
-Cho tôi xem lệnh chuyển tiền theo mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
-Tìm history với mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
-Xem chi tiết biến động số dư với mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
-Liệt kê lệnh chuyển tiền mang mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
-Cho tôi xem giao dịch mang mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
-Cho tôi xem history của mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}
-Search biến động số dư theo mã chi nhánh quản lý trực tiếp khách hàng. {{{branch_code}}}</t>
-  </si>
-  <si>
-    <t>Những lệnh chuyển tiền mang kết quả {{{customer_status}}}
-Lọc các biến động số dư của trạng thái {{{customer_status}}}
-Các giao dịch mang trạng thái hiện tại khách hàng {{{customer_status}}}
-Lọc các lệnh chuyển tiền mang kết quả {{{customer_status}}}
-Các lệnh chuyển tiền tại trạng thái hiện tại khách hàng {{{customer_status}}}
-Những biến động số dư theo tình trạng {{{customer_status}}}
-Danh sách history của trạng thái hiện tại khách hàng {{{customer_status}}}
-Các history tại active, inactive, closed... {{{customer_status}}}
-Danh sách biến động số dư của trạng thái {{{customer_status}}}
-Những giao dịch của kết quả {{{customer_status}}}
-Danh sách giao dịch theo kết quả {{{customer_status}}}
-Các lệnh chuyển tiền của tình trạng {{{customer_status}}}
-Danh sách history với trạng thái hiện tại khách hàng {{{customer_status}}}
-Danh sách giao dịch mang trạng thái hiện tại khách hàng {{{customer_status}}}
-Các giao dịch mang tình trạng {{{customer_status}}}</t>
-  </si>
-  <si>
-    <t>Hiển thị biến động số dư theo ngày cấp giấy tờ định danh {{{date_of_issue}}}
-Tìm giao dịch theo ngày cấp giấy tờ định danh {{{date_of_issue}}}
-Kiểm tra history mang ngày cấp giấy tờ định danh {{{date_of_issue}}}
-Search lệnh chuyển tiền tại cmnd/cccd/hộ chiếu {{{date_of_issue}}}
-Tìm lệnh chuyển tiền mang ngày cấp giấy tờ định danh {{{date_of_issue}}}
-Xem chi tiết biến động số dư mang cmnd/cccd/hộ chiếu {{{date_of_issue}}}
-Xem chi tiết biến động số dư tại cmnd/cccd/hộ chiếu {{{date_of_issue}}}
-Liệt kê lệnh chuyển tiền theo ngày cấp giấy tờ định danh {{{date_of_issue}}}
-Xem chi tiết lệnh chuyển tiền của ngày cấp giấy tờ định danh {{{date_of_issue}}}
-Liệt kê lệnh chuyển tiền của cmnd/cccd/hộ chiếu {{{date_of_issue}}}
-Liệt kê giao dịch mang cmnd/cccd/hộ chiếu {{{date_of_issue}}}
-Kiểm tra lệnh chuyển tiền với ngày cấp giấy tờ định danh {{{date_of_issue}}}
-Liệt kê history theo ngày cấp giấy tờ định danh {{{date_of_issue}}}
-Hiển thị history của ngày cấp giấy tờ định danh {{{date_of_issue}}}
-Xem chi tiết biến động số dư mang ngày cấp giấy tờ định danh {{{date_of_issue}}}</t>
-  </si>
-  <si>
-    <t>Xem chi tiết biến động số dư tại số {{{identify_id}}}
-Tra cứu giao dịch tại mã {{{identify_id}}}
-Kiểm tra biến động số dư có mã {{{identify_id}}}
-Tìm lệnh chuyển tiền tại số cmnd, cccd hoặc hộ chiếu {{{identify_id}}}
-Tra cứu giao dịch của số {{{identify_id}}}
-Cho tôi xem giao dịch với id {{{identify_id}}}
-Tra cứu biến động số dư theo số {{{identify_id}}}
-Hiển thị giao dịch mang id {{{identify_id}}}
-Tra cứu giao dịch tại số {{{identify_id}}}
-Search lệnh chuyển tiền với số cmnd, cccd hoặc hộ chiếu {{{identify_id}}}
-Tìm biến động số dư với số {{{identify_id}}}
-Hiển thị biến động số dư mang số giấy tờ định danh {{{identify_id}}}
-Cho tôi xem history có số cmnd, cccd hoặc hộ chiếu {{{identify_id}}}
-Liệt kê lệnh chuyển tiền của mã {{{identify_id}}}
-mã {{{identify_id}}} là bao nhiêu</t>
-  </si>
-  <si>
-    <t>Xem chi tiết biến động số dư tại số {{{identify_level}}}
-Tra cứu giao dịch tại mã {{{identify_level}}}
-Tra cứu giao dịch có cấp độ định danh {{{identify_level}}}
-Tra cứu lệnh chuyển tiền theo cấp độ định danh {{{identify_level}}}
-Kiểm tra biến động số dư có mã {{{identify_level}}}
-Tra cứu giao dịch của số {{{identify_level}}}
-Cho tôi xem giao dịch với id {{{identify_level}}}
-Tra cứu biến động số dư theo số {{{identify_level}}}
-Tìm giao dịch tại cấp độ định danh {{{identify_level}}}
-Tra cứu giao dịch tại số {{{identify_level}}}
-Hiển thị giao dịch mang id {{{identify_level}}}
-Tìm lệnh chuyển tiền có cấp độ định danh {{{identify_level}}}
-Cho tôi xem history với cấp độ định danh {{{identify_level}}}
-Tìm biến động số dư với số {{{identify_level}}}
-Hiển thị biến động số dư với ví dụ: đã xác thực - ekyc, chưa xác thực {{{identify_level}}}</t>
-  </si>
-  <si>
-    <t>Xem chi tiết biến động số dư tại số {{{identify_name}}}
-Tra cứu giao dịch tại mã {{{identify_name}}}
-Hiển thị history có ví dụ: "identity card", "passport" {{{identify_name}}}
-Cho tôi xem biến động số dư của ví dụ: "identity card", "passport" {{{identify_name}}}
-Kiểm tra biến động số dư có mã {{{identify_name}}}
-Tra cứu giao dịch của số {{{identify_name}}}
-Cho tôi xem giao dịch với id {{{identify_name}}}
-Tra cứu biến động số dư theo số {{{identify_name}}}
-Xem chi tiết lệnh chuyển tiền mang ví dụ: "identity card", "passport" {{{identify_name}}}
-Hiển thị giao dịch mang id {{{identify_name}}}
-Tra cứu giao dịch tại số {{{identify_name}}}
-Liệt kê lệnh chuyển tiền mang loại giấy tờ định danh {{{identify_name}}}
-Tìm biến động số dư với số {{{identify_name}}}
-Liệt kê lệnh chuyển tiền của mã {{{identify_name}}}
-Search giao dịch theo ví dụ: "identity card", "passport" {{{identify_name}}}</t>
-  </si>
-  <si>
-    <t>Sao kê giao dịch từ ngày {{start_date}} đến {{end_date}}
-Liệt kê lịch sử trong khoảng thời gian {{start_date}} - {{end_date}}
-Kiểm tra giao dịch phát sinh từ {{start_date}} tới {{end_date}}
-Cho tôi xem biến động số dư giữa {{start_date}} và {{end_date}}</t>
-  </si>
-  <si>
-    <t>Tính tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. của các giao dịch có cif_type là {{cif_type}}
-Xem tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. theo cif_type {{cif_type}}
-Tính tổng phí của các giao dịch có cif_type là {{cif_type}}
-Xem tổng phí theo cif_type {{cif_type}}
-Tính tổng tiền phí của các giao dịch có cif_type là {{cif_type}}
-Xem tổng tiền phí theo cif_type {{cif_type}}
-Tổng cộng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. của các giao dịch có cif_type là {{cif_type}}
-Xem tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. theo cif_type {{cif_type}}
-Tổng cộng phí của các giao dịch có cif_type là {{cif_type}}
-Xem tổng phí theo cif_type {{cif_type}}
-Tổng cộng tiền phí của các giao dịch có cif_type là {{cif_type}}
-Xem tổng tiền phí theo cif_type {{cif_type}}
-Thống kê đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. của các giao dịch có cif_type là {{cif_type}}
-Xem tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. theo cif_type {{cif_type}}
-Thống kê phí của các giao dịch có cif_type là {{cif_type}}
-Xem tổng phí theo cif_type {{cif_type}}
-Thống kê tiền phí của các giao dịch có cif_type là {{cif_type}}
-Xem tổng tiền phí theo cif_type {{cif_type}}
-Cộng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. của các giao dịch có cif_type là {{cif_type}}
-Xem tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. theo cif_type {{cif_type}}
-Cộng phí của các giao dịch có cif_type là {{cif_type}}
-Xem tổng phí theo cif_type {{cif_type}}
-Cộng tiền phí của các giao dịch có cif_type là {{cif_type}}
-Xem tổng tiền phí theo cif_type {{cif_type}}
-Xem tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. của các giao dịch có cif_type là {{cif_type}}
-Xem tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. theo cif_type {{cif_type}}
-Xem tổng phí của các giao dịch có cif_type là {{cif_type}}
-Xem tổng phí theo cif_type {{cif_type}}
-Xem tổng tiền phí của các giao dịch có cif_type là {{cif_type}}
-Xem tổng tiền phí theo cif_type {{cif_type}}</t>
-  </si>
-  <si>
-    <t>Xem chi tiết biến động số dư tại số {{{nationality_id}}}
-Tra cứu giao dịch tại mã {{{nationality_id}}}
-Kiểm tra biến động số dư có mã {{{nationality_id}}}
-Tra cứu giao dịch của số {{{nationality_id}}}
-Cho tôi xem giao dịch với id {{{nationality_id}}}
-Tra cứu biến động số dư theo số {{{nationality_id}}}
-Kiểm tra lệnh chuyển tiền có ví dụ: vn, us, jp {{{nationality_id}}}
-Hiển thị giao dịch mang id {{{nationality_id}}}
-Tra cứu giao dịch tại số {{{nationality_id}}}
-Tra cứu biến động số dư của ví dụ: vn, us, jp {{{nationality_id}}}
-Search biến động số dư theo mã quốc tịch {{{nationality_id}}}
-Tìm giao dịch của ví dụ: vn, us, jp {{{nationality_id}}}
-Kiểm tra history mang ví dụ: vn, us, jp {{{nationality_id}}}
-Tìm biến động số dư với số {{{nationality_id}}}
-Liệt kê lệnh chuyển tiền của mã {{{nationality_id}}}</t>
-  </si>
-  <si>
-    <t>Xem chi tiết biến động số dư tại số {{{place_id}}}
-Tra cứu giao dịch tại mã {{{place_id}}}
-Kiểm tra biến động số dư có mã {{{place_id}}}
-Tra cứu giao dịch của số {{{place_id}}}
-Cho tôi xem giao dịch với id {{{place_id}}}
-Liệt kê giao dịch với mã vùng/địa điểm cư trú. {{{place_id}}}
-Tra cứu biến động số dư theo số {{{place_id}}}
-Hiển thị giao dịch mang id {{{place_id}}}
-Tra cứu giao dịch tại số {{{place_id}}}
-Search biến động số dư tại mã vùng/địa điểm cư trú. {{{place_id}}}
-Tìm biến động số dư với số {{{place_id}}}
-Liệt kê lệnh chuyển tiền của mã {{{place_id}}}
-mã {{{place_id}}} là bao nhiêu
-Tra cứu history theo mã vùng/địa điểm cư trú. {{{place_id}}}
-Tra cứu lệnh chuyển tiền tại mã {{{place_id}}}</t>
-  </si>
-  <si>
-    <t>Cho tôi xem giao dịch theo ví dụ: ca tp. hà nội {{{place_of_issue}}}
-Liệt kê lệnh chuyển tiền mang ví dụ: ca tp. hà nội {{{place_of_issue}}}
-Liệt kê history tại nơi cấp giấy tờ định danh {{{place_of_issue}}}
-Cho tôi xem biến động số dư theo ví dụ: ca tp. hà nội {{{place_of_issue}}}
-Search history mang nơi cấp giấy tờ định danh {{{place_of_issue}}}
-Tìm lệnh chuyển tiền theo nơi cấp giấy tờ định danh {{{place_of_issue}}}
-Cho tôi xem history mang ví dụ: ca tp. hà nội {{{place_of_issue}}}
-Xem chi tiết biến động số dư tại ví dụ: ca tp. hà nội {{{place_of_issue}}}
-Xem chi tiết giao dịch mang nơi cấp giấy tờ định danh {{{place_of_issue}}}
-Cho tôi xem history có ví dụ: ca tp. hà nội {{{place_of_issue}}}
-Cho tôi xem giao dịch của ví dụ: ca tp. hà nội {{{place_of_issue}}}
-Kiểm tra history theo ví dụ: ca tp. hà nội {{{place_of_issue}}}
-Kiểm tra history của ví dụ: ca tp. hà nội {{{place_of_issue}}}
-Liệt kê lệnh chuyển tiền của nơi cấp giấy tờ định danh {{{place_of_issue}}}
-Tìm giao dịch với ví dụ: ca tp. hà nội {{{place_of_issue}}}</t>
-  </si>
-  <si>
-    <t>Xem chi tiết biến động số dư tại số {{{unique_id}}}
-Tra cứu giao dịch tại mã {{{unique_id}}}
-Kiểm tra biến động số dư có mã {{{unique_id}}}
-Tìm history theo mã định danh duy nhất {{{unique_id}}}
-Tra cứu giao dịch của số {{{unique_id}}}
-Cho tôi xem giao dịch với id {{{unique_id}}}
-Tra cứu biến động số dư theo số {{{unique_id}}}
-Tìm giao dịch với thường đối soát liên hệ thống {{{unique_id}}}
-Tra cứu giao dịch tại số {{{unique_id}}}
-Hiển thị giao dịch mang id {{{unique_id}}}
-Cho tôi xem biến động số dư với thường đối soát liên hệ thống {{{unique_id}}}
-Tìm biến động số dư với số {{{unique_id}}}
-Liệt kê lệnh chuyển tiền của mã {{{unique_id}}}
-Liệt kê biến động số dư mang mã định danh duy nhất {{{unique_id}}}
-mã {{{unique_id}}} là bao nhiêu</t>
-  </si>
-  <si>
-    <t>Tìm giao dịch theo giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
-Xem chi tiết giao dịch của giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
-Kiểm tra lệnh chuyển tiền theo giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
-Hiển thị lệnh chuyển tiền mang giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
-Tìm history của giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
-Tra cứu biến động số dư mang giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
-Cho tôi xem lệnh chuyển tiền theo giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
-Cho tôi xem history với giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
-Cho tôi xem giao dịch tại giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
-Xem chi tiết lệnh chuyển tiền của giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
-Liệt kê giao dịch tại giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
-Tra cứu giao dịch mang giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
-Kiểm tra history theo giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
-Hiển thị lệnh chuyển tiền theo giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}
-Xem chi tiết lệnh chuyển tiền có giá trị đặc trưng định danh duy nhất khách hàng. {{{unique_value}}}</t>
-  </si>
-  <si>
-    <t>Những lệnh chuyển tiền mang kết quả {{{status}}}
-Lọc các biến động số dư của trạng thái {{{status}}}
-Lọc các lệnh chuyển tiền mang kết quả {{{status}}}
-Danh sách lệnh chuyển tiền có trạng thái bản ghi {{{status}}}
-Lọc các lệnh chuyển tiền theo ví dụ: 1-hiệu lực, 0-hết hiệu lực {{{status}}}
-Các biến động số dư theo trạng thái bản ghi {{{status}}}
-Các lệnh chuyển tiền có trạng thái bản ghi {{{status}}}
-Những biến động số dư theo tình trạng {{{status}}}
-Lọc các history của trạng thái bản ghi {{{status}}}
-Các lệnh chuyển tiền của trạng thái bản ghi {{{status}}}
-Các lệnh chuyển tiền mang trạng thái bản ghi {{{status}}}
-Danh sách biến động số dư của trạng thái {{{status}}}
-Những giao dịch của kết quả {{{status}}}
-Lọc các biến động số dư của trạng thái bản ghi {{{status}}}
-Danh sách giao dịch theo kết quả {{{status}}}</t>
-  </si>
-  <si>
-    <t>Những lệnh chuyển tiền mang kết quả {{{old_customer_status}}}
-Lọc các biến động số dư của trạng thái {{{old_customer_status}}}
-Những lệnh chuyển tiền tại trước khi thay đổi {{{old_customer_status}}}
-Danh sách lệnh chuyển tiền theo trước khi thay đổi {{{old_customer_status}}}
-Danh sách lệnh chuyển tiền tại trước khi thay đổi {{{old_customer_status}}}
-Lọc các giao dịch tại trạng thái cũ khách hàng {{{old_customer_status}}}
-Danh sách giao dịch theo trước khi thay đổi {{{old_customer_status}}}
-Lọc các lệnh chuyển tiền mang kết quả {{{old_customer_status}}}
-Danh sách biến động số dư theo trạng thái cũ khách hàng {{{old_customer_status}}}
-Những biến động số dư theo tình trạng {{{old_customer_status}}}
-Lọc các biến động số dư mang trước khi thay đổi {{{old_customer_status}}}
-Danh sách history với trước khi thay đổi {{{old_customer_status}}}
-Danh sách biến động số dư của trạng thái {{{old_customer_status}}}
-Những giao dịch của kết quả {{{old_customer_status}}}
-Những giao dịch có trạng thái cũ khách hàng {{{old_customer_status}}}</t>
-  </si>
-  <si>
-    <t>Các history có sau khi cập nhật {{{new_customer_status}}}
-Những lệnh chuyển tiền mang kết quả {{{new_customer_status}}}
-Lọc các biến động số dư của trạng thái {{{new_customer_status}}}
-Lọc các giao dịch mang trạng thái mới khách hàng {{{new_customer_status}}}
-Lọc các biến động số dư có trạng thái mới khách hàng {{{new_customer_status}}}
-Lọc các lệnh chuyển tiền mang kết quả {{{new_customer_status}}}
-Các giao dịch mang trạng thái mới khách hàng {{{new_customer_status}}}
-Những biến động số dư theo tình trạng {{{new_customer_status}}}
-Lọc các giao dịch với sau khi cập nhật {{{new_customer_status}}}
-Danh sách lệnh chuyển tiền có sau khi cập nhật {{{new_customer_status}}}
-Danh sách biến động số dư của trạng thái {{{new_customer_status}}}
-Những giao dịch của kết quả {{{new_customer_status}}}
-Danh sách biến động số dư mang trạng thái mới khách hàng {{{new_customer_status}}}
-Danh sách giao dịch theo kết quả {{{new_customer_status}}}
-Những biến động số dư của sau khi cập nhật {{{new_customer_status}}}</t>
-  </si>
-  <si>
-    <t>Hiển thị lệnh chuyển tiền tại cmnd/cccd {{{unique_image_front}}}
-Hiển thị lệnh chuyển tiền theo đường dẫn ảnh mặt trước giấy tờ định danh {{{unique_image_front}}}
-Liệt kê giao dịch có đường dẫn ảnh mặt trước giấy tờ định danh {{{unique_image_front}}}
-Kiểm tra biến động số dư với cmnd/cccd {{{unique_image_front}}}
-Hiển thị lệnh chuyển tiền theo cmnd/cccd {{{unique_image_front}}}
-Tìm lệnh chuyển tiền của cmnd/cccd {{{unique_image_front}}}
-Cho tôi xem lệnh chuyển tiền tại cmnd/cccd {{{unique_image_front}}}
-đường dẫn ảnh mặt trước giấy tờ định danh {{{unique_image_front}}} là bao nhiêu
-Search lệnh chuyển tiền theo đường dẫn ảnh mặt trước giấy tờ định danh {{{unique_image_front}}}
-Tra cứu giao dịch theo cmnd/cccd {{{unique_image_front}}}
-Tìm biến động số dư theo cmnd/cccd {{{unique_image_front}}}
-Hiển thị lệnh chuyển tiền có đường dẫn ảnh mặt trước giấy tờ định danh {{{unique_image_front}}}
-Xem chi tiết biến động số dư với đường dẫn ảnh mặt trước giấy tờ định danh {{{unique_image_front}}}
-Hiển thị giao dịch mang đường dẫn ảnh mặt trước giấy tờ định danh {{{unique_image_front}}}
-Cho tôi xem biến động số dư có đường dẫn ảnh mặt trước giấy tờ định danh {{{unique_image_front}}}</t>
-  </si>
-  <si>
-    <t>Hiển thị lệnh chuyển tiền mang đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
-Xem chi tiết giao dịch theo đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
-Kiểm tra history mang đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
-Liệt kê giao dịch theo đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
-Cho tôi xem lệnh chuyển tiền có đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
-Cho tôi xem history của đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
-Liệt kê history mang đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
-Search giao dịch mang đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
-Search history tại đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
-Tra cứu biến động số dư mang đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
-Tra cứu lệnh chuyển tiền theo đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
-Liệt kê biến động số dư có đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
-Tra cứu history tại đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
-Tìm giao dịch theo đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}
-Cho tôi xem lệnh chuyển tiền mang đường dẫn ảnh mặt sau giấy tờ định danh. {{{unique_image_back}}}</t>
-  </si>
-  <si>
-    <t>id, tra cứu, tìm kiếm</t>
-  </si>
-  <si>
-    <t>cif_no, tra cứu, tìm kiếm</t>
-  </si>
-  <si>
-    <t>customer_id, tra cứu, tìm kiếm</t>
-  </si>
-  <si>
-    <t>customer_no, tra cứu, tìm kiếm</t>
-  </si>
-  <si>
-    <t>system_id, tra cứu, tìm kiếm</t>
-  </si>
-  <si>
-    <t>cif_branch, tra cứu, tìm kiếm</t>
-  </si>
-  <si>
-    <t>cif_type, danh sách, lọc</t>
-  </si>
-  <si>
-    <t>branch_code, tra cứu, tìm kiếm</t>
-  </si>
-  <si>
-    <t>customer_status, danh sách, lọc</t>
-  </si>
-  <si>
-    <t>date_of_issue, tra cứu, tìm kiếm</t>
-  </si>
-  <si>
-    <t>identify_id, tra cứu, tìm kiếm</t>
-  </si>
-  <si>
-    <t>identify_level, tra cứu, tìm kiếm</t>
-  </si>
-  <si>
-    <t>identify_name, tra cứu, tìm kiếm</t>
-  </si>
-  <si>
-    <t>thời gian, ngày tháng, sao kê</t>
+    <t>customer | Tra cứu theo id tự tăng, khóa chính</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu theo mã định danh khách hàng</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu theo số</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu theo nếu dữ liệu được đẩy từ khác sang</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu theo chi nhánh nơi mở/quản lý mã cif này.</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo kiểu</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu theo code</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo kết quả</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu theo ngày cấp giấy tờ định danh</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu theo số cmnd, cccd hoặc hộ chiếu</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu theo cấp độ định danh</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu theo họ tên</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo thời gian (thời gian)</t>
+  </si>
+  <si>
+    <t>customer | Thống kê đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. theo loại</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu theo mã vùng/địa điểm cư trú.</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu theo ví dụ: ca tp. hà nội</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu theo thường đối soát liên hệ thống</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu theo giá trị đặc trưng định danh duy nhất khách hàng.</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo trạng thái bản ghi</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo thời gian (ngày tháng năm sinh.)</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo trước khi thay đổi</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu theo đường dẫn ảnh mặt trước giấy tờ định danh</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu theo đường dẫn ảnh mặt sau giấy tờ định danh.</t>
+  </si>
+  <si>
+    <t>customer | Lọc loại theo Thời gian</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác khách hàng dựa trên id tự tăng, khóa chính</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác khách hàng dựa trên mã định danh khách hàng</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác khách hàng dựa trên số</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác khách hàng dựa trên nếu dữ liệu được đẩy từ khác sang</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác khách hàng dựa trên chi nhánh nơi mở/quản lý mã cif này.</t>
+  </si>
+  <si>
+    <t>Liệt kê danh sách khách hàng theo nhóm kiểu</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác khách hàng dựa trên code</t>
+  </si>
+  <si>
+    <t>Liệt kê danh sách khách hàng theo nhóm kết quả</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác khách hàng dựa trên ngày cấp giấy tờ định danh</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác khách hàng dựa trên số cmnd, cccd hoặc hộ chiếu</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác khách hàng dựa trên cấp độ định danh</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác khách hàng dựa trên họ tên</t>
+  </si>
+  <si>
+    <t>Sao kê lịch sử khách hàng trong khoảng thời gian</t>
+  </si>
+  <si>
+    <t>Tính tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. được phân loại bởi loại</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác khách hàng dựa trên mã vùng/địa điểm cư trú.</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác khách hàng dựa trên ví dụ: ca tp. hà nội</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác khách hàng dựa trên thường đối soát liên hệ thống</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác khách hàng dựa trên giá trị đặc trưng định danh duy nhất khách hàng.</t>
+  </si>
+  <si>
+    <t>Liệt kê danh sách khách hàng theo nhóm trạng thái bản ghi</t>
+  </si>
+  <si>
+    <t>Liệt kê danh sách khách hàng theo nhóm trước khi thay đổi</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác khách hàng dựa trên đường dẫn ảnh mặt trước giấy tờ định danh</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác khách hàng dựa trên đường dẫn ảnh mặt sau giấy tờ định danh.</t>
+  </si>
+  <si>
+    <t>Kết hợp lọc theo loại và khoảng ngày tháng</t>
+  </si>
+  <si>
+    <t>Thông tin về khách hàng số 56041
+Tra cứu khách hàng theo id tự tăng, khóa chính 79364
+Check id tự tăng, khóa chính 9662
+Tìm kiếm khách hàng ứng với số 53798
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có id tự tăng, khóa chính là 35196
+id tự tăng, khóa chính 38801 là của ai?
+khách hàng 8977
+Xem chi tiết 22398
+Hãy hiển thị dữ liệu bản ghi khách hàng với id tự tăng, khóa chính 33286</t>
+  </si>
+  <si>
+    <t>Hãy hiển thị dữ liệu bản ghi khách hàng với mã định danh khách hàng 61867503
+Xem chi tiết 41847154
+khách hàng 69791166
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có mã định danh khách hàng là 73084159
+Tìm kiếm khách hàng ứng với số 74487308
+Thông tin về khách hàng số 94168774
+Check mã định danh khách hàng 38631711
+mã định danh khách hàng 39333607 là của ai?
+Tra cứu khách hàng theo mã định danh khách hàng 63865928</t>
+  </si>
+  <si>
+    <t>khách hàng 87112
+số 87413 là của ai?
+Tìm kiếm khách hàng ứng với số 42845
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có số là 41315
+Thông tin về khách hàng số 4904
+Hãy hiển thị dữ liệu bản ghi khách hàng với số 93316
+Tra cứu khách hàng theo số 62678
+Xem chi tiết 88100
+Check số 32523</t>
+  </si>
+  <si>
+    <t>Tra cứu khách hàng theo số 59445
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có số là 8500
+Xem chi tiết 98263
+Thông tin về khách hàng số 2086
+Hãy hiển thị dữ liệu bản ghi khách hàng với số 84059
+số 58637 là của ai?
+khách hàng 57034
+Tìm kiếm khách hàng ứng với số 99477
+Check số 20357</t>
+  </si>
+  <si>
+    <t>Check nếu dữ liệu được đẩy từ khác sang 93334
+Xem chi tiết 56538
+Tra cứu khách hàng theo nếu dữ liệu được đẩy từ khác sang 26135
+nếu dữ liệu được đẩy từ khác sang 31743 là của ai?
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có nếu dữ liệu được đẩy từ khác sang là 89691
+Tìm kiếm khách hàng ứng với số 7451
+Hãy hiển thị dữ liệu bản ghi khách hàng với nếu dữ liệu được đẩy từ khác sang 53397
+khách hàng 58597
+Thông tin về khách hàng số 90814</t>
+  </si>
+  <si>
+    <t>Tìm kiếm khách hàng ứng với số 62148056
+Hãy hiển thị dữ liệu bản ghi khách hàng với chi nhánh nơi mở/quản lý mã cif này. 74199029
+khách hàng 72995189
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có chi nhánh nơi mở/quản lý mã cif này. là 54539025
+chi nhánh nơi mở/quản lý mã cif này. 50612986 là của ai?
+Tra cứu khách hàng theo chi nhánh nơi mở/quản lý mã cif này. 25750731
+Check chi nhánh nơi mở/quản lý mã cif này. 33686468
+Xem chi tiết 32278866
+Thông tin về khách hàng số 25133949</t>
+  </si>
+  <si>
+    <t>Cho xem danh sách khách hàng tại
+Hãy liệt kê danh sách các khách hàng có kiểu là tại
+Tìm tất cả khách hàng loại mà
+Danh sách đến
+Trích xuất báo cáo các khách hàng thuộc loại thay
+Lọc các khách hàng đang ở trạng thái đã
+Những khách hàng nào là thế?</t>
+  </si>
+  <si>
+    <t>code 93584 là của ai?
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có code là 64860
+Xem chi tiết 35263
+Check code 42429
+Tra cứu khách hàng theo code 39077
+Thông tin về khách hàng số 50474
+Hãy hiển thị dữ liệu bản ghi khách hàng với code 31797
+khách hàng 95788
+Tìm kiếm khách hàng ứng với số 95460</t>
+  </si>
+  <si>
+    <t>Hãy liệt kê danh sách các khách hàng có kết quả là hơn
+Lọc các khách hàng đang ở trạng thái từng
+Tìm tất cả khách hàng loại mà
+Danh sách lớn
+Cho xem danh sách khách hàng với
+Những khách hàng nào là người?
+Trích xuất báo cáo các khách hàng thuộc loại tại</t>
+  </si>
+  <si>
+    <t>Check ngày cấp giấy tờ định danh 90049
+Thông tin về khách hàng số 50821
+khách hàng 94661
+Tra cứu khách hàng theo ngày cấp giấy tờ định danh 92762
+Xem chi tiết 8475
+Tìm kiếm khách hàng ứng với số 18037
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có ngày cấp giấy tờ định danh là 15057
+ngày cấp giấy tờ định danh 90260 là của ai?
+Hãy hiển thị dữ liệu bản ghi khách hàng với ngày cấp giấy tờ định danh 90650</t>
+  </si>
+  <si>
+    <t>Vui lòng Tra cứu thông tin chi tiết của khách hàng có số cmnd, cccd hoặc hộ chiếu là 76851
+số cmnd, cccd hoặc hộ chiếu 41673 là của ai?
+khách hàng 31045
+Hãy hiển thị dữ liệu bản ghi khách hàng với số cmnd, cccd hoặc hộ chiếu 50284
+Check số cmnd, cccd hoặc hộ chiếu 62549
+Thông tin về khách hàng số 80472
+Xem chi tiết 43428
+Tìm kiếm khách hàng ứng với số 57645
+Tra cứu khách hàng theo số cmnd, cccd hoặc hộ chiếu 8523</t>
+  </si>
+  <si>
+    <t>Tìm kiếm khách hàng ứng với số 63848
+Tra cứu khách hàng theo cấp độ định danh 87615
+Check cấp độ định danh 19702
+Thông tin về khách hàng số 33576
+cấp độ định danh 27758 là của ai?
+Xem chi tiết 1691
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có cấp độ định danh là 48733
+khách hàng 98370
+Hãy hiển thị dữ liệu bản ghi khách hàng với cấp độ định danh 67285</t>
+  </si>
+  <si>
+    <t>Tìm kiếm khách hàng ứng với số Ông Quang Trần
+Xem chi tiết Phương Phú Dương
+Hãy hiển thị dữ liệu bản ghi khách hàng với họ tên Dương Bùi
+Thông tin về khách hàng số Linh Đặng
+họ tên Vi Trần là của ai?
+Tra cứu khách hàng theo họ tên Quý ông Trọng Vũ
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có họ tên là Hải Thị Mai
+Check họ tên Nhật Hoàng Hoàng
+khách hàng Kim Hải Mai</t>
+  </si>
+  <si>
+    <t>Truy xuất lịch sử khách hàng trong khoảng thời gian từ 2025-05-31 đến hôm nay
+Kiểm tra khách hàng trong ngày 2025-06-02
+Những khách hàng nào diễn ra từ 2025-12-25 đến hôm nay?
+Liệt kê các giao dịch phát sinh từ ngày 2025-06-02 tới ngày hôm nay
+Lịch sử khách hàng 2025-04-07 đến hôm nay
+Xem biến động khách hàng giữa 2025-04-06 và hôm nay
+Sao kê khách hàng từ 2025-11-29 - hôm nay</t>
+  </si>
+  <si>
+    <t>Hãy tính toán tổng giá trị đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. cho nhóm 19300000
+khách hàng 3720000 có tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. là mấy?
+Cộng hết đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. của các giao dịch 3160000
+Tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. của khách hàng 33800000 là bao nhiêu?
+Tính tổng tiền đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. theo loại 16150000
+Thống kê tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. của các khách hàng được phân loại theo loại 15950000</t>
+  </si>
+  <si>
+    <t>khách hàng 69682
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có số là 11514
+Thông tin về khách hàng số 51458
+Check số 17408
+Tìm kiếm khách hàng ứng với số 53622
+Hãy hiển thị dữ liệu bản ghi khách hàng với số 6199
+số 47661 là của ai?
+Tra cứu khách hàng theo số 87522
+Xem chi tiết 96449</t>
+  </si>
+  <si>
+    <t>khách hàng 52617
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có mã vùng/địa điểm cư trú. là 5425
+mã vùng/địa điểm cư trú. 18335 là của ai?
+Tra cứu khách hàng theo mã vùng/địa điểm cư trú. 64992
+Thông tin về khách hàng số 42179
+Tìm kiếm khách hàng ứng với số 56854
+Hãy hiển thị dữ liệu bản ghi khách hàng với mã vùng/địa điểm cư trú. 69133
+Xem chi tiết 80871
+Check mã vùng/địa điểm cư trú. 36095</t>
+  </si>
+  <si>
+    <t>Check ví dụ: ca tp. hà nội 26383
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có ví dụ: ca tp. hà nội là 25139
+Tìm kiếm khách hàng ứng với số 74867
+khách hàng 67810
+ví dụ: ca tp. hà nội 99840 là của ai?
+Hãy hiển thị dữ liệu bản ghi khách hàng với ví dụ: ca tp. hà nội 48256
+Tra cứu khách hàng theo ví dụ: ca tp. hà nội 75876
+Thông tin về khách hàng số 59980
+Xem chi tiết 1985</t>
+  </si>
+  <si>
+    <t>Xem chi tiết 77127
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có thường đối soát liên hệ thống là 86325
+Hãy hiển thị dữ liệu bản ghi khách hàng với thường đối soát liên hệ thống 88693
+Tìm kiếm khách hàng ứng với số 31029
+Check thường đối soát liên hệ thống 78031
+Tra cứu khách hàng theo thường đối soát liên hệ thống 68463
+Thông tin về khách hàng số 45360
+khách hàng 63348
+thường đối soát liên hệ thống 77526 là của ai?</t>
+  </si>
+  <si>
+    <t>Tìm kiếm khách hàng ứng với số 4467
+Tra cứu khách hàng theo giá trị đặc trưng định danh duy nhất khách hàng. 11849
+Hãy hiển thị dữ liệu bản ghi khách hàng với giá trị đặc trưng định danh duy nhất khách hàng. 80052
+Check giá trị đặc trưng định danh duy nhất khách hàng. 96054
+Thông tin về khách hàng số 25033
+giá trị đặc trưng định danh duy nhất khách hàng. 25709 là của ai?
+khách hàng 42661
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có giá trị đặc trưng định danh duy nhất khách hàng. là 36441
+Xem chi tiết 63835</t>
+  </si>
+  <si>
+    <t>Những khách hàng nào là sau?
+Cho xem danh sách khách hàng khiến
+Lọc các khách hàng đang ở trạng thái vài
+Hãy liệt kê danh sách các khách hàng có trạng thái bản ghi là cách
+Tìm tất cả khách hàng loại rất
+Trích xuất báo cáo các khách hàng thuộc loại với
+Danh sách tại</t>
+  </si>
+  <si>
+    <t>Truy xuất lịch sử khách hàng trong khoảng thời gian từ 2025-07-21 đến hôm nay
+Kiểm tra khách hàng trong ngày 2025-11-16
+Liệt kê các giao dịch phát sinh từ ngày 2025-12-27 tới ngày hôm nay
+Lịch sử khách hàng 2025-04-22 đến hôm nay
+Sao kê khách hàng từ 2025-08-20 - hôm nay
+Những khách hàng nào diễn ra từ 2025-08-17 đến hôm nay?
+Xem biến động khách hàng giữa 2025-04-06 và hôm nay</t>
+  </si>
+  <si>
+    <t>Cho xem danh sách khách hàng có
+Lọc các khách hàng đang ở trạng thái cũng
+Trích xuất báo cáo các khách hàng thuộc loại đến
+Danh sách tự
+Hãy liệt kê danh sách các khách hàng có trước khi thay đổi là như
+Những khách hàng nào là thế?
+Tìm tất cả khách hàng loại bên</t>
+  </si>
+  <si>
+    <t>Danh sách bên
+Những khách hàng nào là theo?
+Trích xuất báo cáo các khách hàng thuộc loại cho
+Tìm tất cả khách hàng loại như
+Hãy liệt kê danh sách các khách hàng có kết quả là bạn
+Lọc các khách hàng đang ở trạng thái mà
+Cho xem danh sách khách hàng sau</t>
+  </si>
+  <si>
+    <t>Tra cứu khách hàng theo đường dẫn ảnh mặt trước giấy tờ định danh 35188
+Xem chi tiết 69623
+Tìm kiếm khách hàng ứng với số 62936
+Check đường dẫn ảnh mặt trước giấy tờ định danh 54618
+Thông tin về khách hàng số 11016
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có đường dẫn ảnh mặt trước giấy tờ định danh là 32731
+Hãy hiển thị dữ liệu bản ghi khách hàng với đường dẫn ảnh mặt trước giấy tờ định danh 40834
+khách hàng 56396
+đường dẫn ảnh mặt trước giấy tờ định danh 48273 là của ai?</t>
+  </si>
+  <si>
+    <t>Tìm kiếm khách hàng ứng với số 1490
+Tra cứu khách hàng theo đường dẫn ảnh mặt sau giấy tờ định danh. 9587
+Hãy hiển thị dữ liệu bản ghi khách hàng với đường dẫn ảnh mặt sau giấy tờ định danh. 57172
+khách hàng 49257
+Xem chi tiết 25209
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có đường dẫn ảnh mặt sau giấy tờ định danh. là 17489
+Check đường dẫn ảnh mặt sau giấy tờ định danh. 49040
+đường dẫn ảnh mặt sau giấy tờ định danh. 6548 là của ai?
+Thông tin về khách hàng số 76563</t>
+  </si>
+  <si>
+    <t>Lọc các khách hàng làm diễn ra từ 2026-01-02 đến hôm nay
+Xem khách hàng có loại là khiến trong khoảng 2025-12-24 - hôm nay
+Sao kê khách hàng loại gần từ ngày 2025-08-18 tới hôm nay
+Liệt kê khách hàng trong phát sinh ngày 2025-02-27
+Tìm khách hàng khi hôm 2025-05-22</t>
+  </si>
+  <si>
+    <t>id, id tự tăng, khóa chính, tìm kiếm</t>
+  </si>
+  <si>
+    <t>cif_no, mã định danh khách hàng, tìm kiếm</t>
+  </si>
+  <si>
+    <t>customer_id, số, tìm kiếm</t>
+  </si>
+  <si>
+    <t>customer_no, số, tìm kiếm</t>
+  </si>
+  <si>
+    <t>system_id, nếu dữ liệu được đẩy từ khác sang, tìm kiếm</t>
+  </si>
+  <si>
+    <t>cif_branch, chi nhánh nơi mở/quản lý mã cif này., tìm kiếm</t>
+  </si>
+  <si>
+    <t>cif_type, kiểu, danh sách</t>
+  </si>
+  <si>
+    <t>branch_code, code, tìm kiếm</t>
+  </si>
+  <si>
+    <t>customer_status, kết quả, danh sách</t>
+  </si>
+  <si>
+    <t>date_of_issue, ngày cấp giấy tờ định danh, tìm kiếm</t>
+  </si>
+  <si>
+    <t>identify_id, số cmnd, cccd hoặc hộ chiếu, tìm kiếm</t>
+  </si>
+  <si>
+    <t>identify_level, cấp độ định danh, tìm kiếm</t>
+  </si>
+  <si>
+    <t>identify_name, họ tên, tìm kiếm</t>
+  </si>
+  <si>
+    <t>init_date, thời gian, ngày tháng</t>
   </si>
   <si>
     <t>tổng is_fee_default, thống kê</t>
   </si>
   <si>
-    <t>nationality_id, tra cứu, tìm kiếm</t>
-  </si>
-  <si>
-    <t>place_id, tra cứu, tìm kiếm</t>
-  </si>
-  <si>
-    <t>place_of_issue, tra cứu, tìm kiếm</t>
-  </si>
-  <si>
-    <t>unique_id, tra cứu, tìm kiếm</t>
-  </si>
-  <si>
-    <t>unique_value, tra cứu, tìm kiếm</t>
-  </si>
-  <si>
-    <t>status, danh sách, lọc</t>
-  </si>
-  <si>
-    <t>old_customer_status, danh sách, lọc</t>
-  </si>
-  <si>
-    <t>new_customer_status, danh sách, lọc</t>
-  </si>
-  <si>
-    <t>unique_image_front, tra cứu, tìm kiếm</t>
-  </si>
-  <si>
-    <t>unique_image_back, tra cứu, tìm kiếm</t>
+    <t>nationality_id, số, tìm kiếm</t>
+  </si>
+  <si>
+    <t>place_id, mã vùng/địa điểm cư trú., tìm kiếm</t>
+  </si>
+  <si>
+    <t>place_of_issue, ví dụ: ca tp. hà nội, tìm kiếm</t>
+  </si>
+  <si>
+    <t>unique_id, thường đối soát liên hệ thống, tìm kiếm</t>
+  </si>
+  <si>
+    <t>unique_value, giá trị đặc trưng định danh duy nhất khách hàng., tìm kiếm</t>
+  </si>
+  <si>
+    <t>status, trạng thái bản ghi, danh sách</t>
+  </si>
+  <si>
+    <t>date_of_birth, thời gian, ngày tháng</t>
+  </si>
+  <si>
+    <t>old_customer_status, trước khi thay đổi, danh sách</t>
+  </si>
+  <si>
+    <t>new_customer_status, kết quả, danh sách</t>
+  </si>
+  <si>
+    <t>unique_image_front, đường dẫn ảnh mặt trước giấy tờ định danh, tìm kiếm</t>
+  </si>
+  <si>
+    <t>unique_image_back, đường dẫn ảnh mặt sau giấy tờ định danh., tìm kiếm</t>
+  </si>
+  <si>
+    <t>cif_type, init_date, lọc đa điều kiện</t>
   </si>
   <si>
     <t>{"raw_text": "SELECT * FROM customer WHERE id = '{{id}}'"}</t>
@@ -764,6 +605,9 @@
   </si>
   <si>
     <t>{"raw_text": "SELECT * FROM customer WHERE unique_image_back = '{{unique_image_back}}'"}</t>
+  </si>
+  <si>
+    <t>{"raw_text": "SELECT * FROM customer WHERE cif_type = '{{cif_type}}' AND init_date BETWEEN '{{start_date}}' AND '{{end_date}}'"}</t>
   </si>
 </sst>
 </file>
@@ -1121,7 +965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1146,13 +990,13 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
         <v>106</v>
@@ -1163,13 +1007,13 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
         <v>107</v>
@@ -1180,13 +1024,13 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
         <v>108</v>
@@ -1194,16 +1038,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
         <v>109</v>
@@ -1211,16 +1055,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
         <v>110</v>
@@ -1228,16 +1072,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
         <v>111</v>
@@ -1245,16 +1089,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
         <v>112</v>
@@ -1262,16 +1106,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
         <v>113</v>
@@ -1279,16 +1123,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
         <v>114</v>
@@ -1296,16 +1140,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
         <v>115</v>
@@ -1313,16 +1157,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E12" t="s">
         <v>116</v>
@@ -1330,16 +1174,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E13" t="s">
         <v>117</v>
@@ -1347,16 +1191,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E14" t="s">
         <v>118</v>
@@ -1364,16 +1208,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D15" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E15" t="s">
         <v>119</v>
@@ -1381,16 +1225,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E16" t="s">
         <v>120</v>
@@ -1398,16 +1242,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E17" t="s">
         <v>121</v>
@@ -1415,16 +1259,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E18" t="s">
         <v>122</v>
@@ -1432,16 +1276,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D19" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E19" t="s">
         <v>123</v>
@@ -1449,16 +1293,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E20" t="s">
         <v>124</v>
@@ -1466,16 +1310,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D21" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E21" t="s">
         <v>125</v>
@@ -1483,16 +1327,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D22" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E22" t="s">
         <v>126</v>
@@ -1500,16 +1344,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E23" t="s">
         <v>127</v>
@@ -1517,16 +1361,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E24" t="s">
         <v>128</v>
@@ -1534,16 +1378,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E25" t="s">
         <v>129</v>
@@ -1551,16 +1395,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E26" t="s">
         <v>130</v>
@@ -1568,19 +1412,36 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D27" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E27" t="s">
         <v>131</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" t="s">
+        <v>105</v>
+      </c>
+      <c r="E28" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
